--- a/research/traditional_assets/database/data/pakistan/pakistan_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_heathcare_information_and_technology.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2377685519053315</v>
+        <v>0.237110973104806</v>
       </c>
       <c r="C2">
-        <v>12.55301358745826</v>
+        <v>12.47040740205548</v>
       </c>
       <c r="D2">
-        <v>12.42101358745826</v>
+        <v>12.46370740205548</v>
       </c>
       <c r="E2">
-        <v>-4.06</v>
+        <v>-3.934699999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1253</v>
       </c>
       <c r="G2">
         <v>0.132</v>
@@ -1439,28 +1439,28 @@
         <v>3.13</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006302590000000001</v>
       </c>
       <c r="N2">
-        <v>3.13</v>
+        <v>3.12369741</v>
       </c>
       <c r="O2">
-        <v>0.9077</v>
+        <v>0.9058722488999998</v>
       </c>
       <c r="P2">
-        <v>2.2223</v>
+        <v>2.2178251611</v>
       </c>
       <c r="Q2">
-        <v>2.942299999999999</v>
+        <v>2.9378251611</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2377685519053315</v>
+        <v>0.2391452960654606</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.182475762201046</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>496.6212303195986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.237110973104806</v>
+        <v>0.2364533943042805</v>
       </c>
       <c r="C3">
-        <v>12.47040740205548</v>
+        <v>12.38809572541292</v>
       </c>
       <c r="D3">
-        <v>12.46370740205548</v>
+        <v>12.50669572541292</v>
       </c>
       <c r="E3">
-        <v>-3.934699999999999</v>
+        <v>-3.8094</v>
       </c>
       <c r="F3">
-        <v>0.1253</v>
+        <v>0.2506</v>
       </c>
       <c r="G3">
         <v>0.132</v>
@@ -1521,28 +1521,28 @@
         <v>3.13</v>
       </c>
       <c r="M3">
-        <v>0.006302590000000001</v>
+        <v>0.01260518</v>
       </c>
       <c r="N3">
-        <v>3.12369741</v>
+        <v>3.11739482</v>
       </c>
       <c r="O3">
-        <v>0.9058722488999998</v>
+        <v>0.9040444978</v>
       </c>
       <c r="P3">
-        <v>2.2178251611</v>
+        <v>2.2133503222</v>
       </c>
       <c r="Q3">
-        <v>2.9378251611</v>
+        <v>2.9333503222</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2391452960654606</v>
+        <v>0.2405501370451842</v>
       </c>
       <c r="T3">
-        <v>1.182475762201046</v>
+        <v>1.191067594751797</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>496.6212303195986</v>
+        <v>248.3106151597993</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2364533943042805</v>
+        <v>0.2357958155037551</v>
       </c>
       <c r="C4">
-        <v>12.38809572541292</v>
+        <v>12.30608161543027</v>
       </c>
       <c r="D4">
-        <v>12.50669572541292</v>
+        <v>12.54998161543027</v>
       </c>
       <c r="E4">
-        <v>-3.8094</v>
+        <v>-3.684099999999999</v>
       </c>
       <c r="F4">
-        <v>0.2506</v>
+        <v>0.3759</v>
       </c>
       <c r="G4">
         <v>0.132</v>
@@ -1603,28 +1603,28 @@
         <v>3.13</v>
       </c>
       <c r="M4">
-        <v>0.01260518</v>
+        <v>0.01890777</v>
       </c>
       <c r="N4">
-        <v>3.11739482</v>
+        <v>3.11109223</v>
       </c>
       <c r="O4">
-        <v>0.9040444978</v>
+        <v>0.9022167466999998</v>
       </c>
       <c r="P4">
-        <v>2.2133503222</v>
+        <v>2.2088754833</v>
       </c>
       <c r="Q4">
-        <v>2.9333503222</v>
+        <v>2.9288754833</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2405501370451842</v>
+        <v>0.2419839438183042</v>
       </c>
       <c r="T4">
-        <v>1.191067594751797</v>
+        <v>1.199836578489163</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>248.3106151597993</v>
+        <v>165.5404101065329</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2357958155037551</v>
+        <v>0.2351382367032296</v>
       </c>
       <c r="C5">
-        <v>12.30608161543027</v>
+        <v>12.22436817248809</v>
       </c>
       <c r="D5">
-        <v>12.54998161543027</v>
+        <v>12.59356817248809</v>
       </c>
       <c r="E5">
-        <v>-3.684099999999999</v>
+        <v>-3.5588</v>
       </c>
       <c r="F5">
-        <v>0.3759</v>
+        <v>0.5012000000000001</v>
       </c>
       <c r="G5">
         <v>0.132</v>
@@ -1685,28 +1685,28 @@
         <v>3.13</v>
       </c>
       <c r="M5">
-        <v>0.01890777</v>
+        <v>0.02521036</v>
       </c>
       <c r="N5">
-        <v>3.11109223</v>
+        <v>3.10478964</v>
       </c>
       <c r="O5">
-        <v>0.9022167466999998</v>
+        <v>0.9003889956</v>
       </c>
       <c r="P5">
-        <v>2.2088754833</v>
+        <v>2.2044006444</v>
       </c>
       <c r="Q5">
-        <v>2.9288754833</v>
+        <v>2.924400644399999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2419839438183042</v>
+        <v>0.2434476215658642</v>
       </c>
       <c r="T5">
-        <v>1.199836578489163</v>
+        <v>1.208788249387723</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>165.5404101065329</v>
+        <v>124.1553075798997</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2351382367032296</v>
+        <v>0.2344806579027041</v>
       </c>
       <c r="C6">
-        <v>12.22436817248809</v>
+        <v>12.14295854018794</v>
       </c>
       <c r="D6">
-        <v>12.59356817248809</v>
+        <v>12.63745854018794</v>
       </c>
       <c r="E6">
-        <v>-3.5588</v>
+        <v>-3.4335</v>
       </c>
       <c r="F6">
-        <v>0.5012000000000001</v>
+        <v>0.6265000000000001</v>
       </c>
       <c r="G6">
         <v>0.132</v>
@@ -1767,28 +1767,28 @@
         <v>3.13</v>
       </c>
       <c r="M6">
-        <v>0.02521036</v>
+        <v>0.03151295</v>
       </c>
       <c r="N6">
-        <v>3.10478964</v>
+        <v>3.09848705</v>
       </c>
       <c r="O6">
-        <v>0.9003889956</v>
+        <v>0.8985612444999999</v>
       </c>
       <c r="P6">
-        <v>2.2044006444</v>
+        <v>2.1999258055</v>
       </c>
       <c r="Q6">
-        <v>2.924400644399999</v>
+        <v>2.9199258055</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2434476215658642</v>
+        <v>0.2449421135817939</v>
       </c>
       <c r="T6">
-        <v>1.208788249387723</v>
+        <v>1.217928376515726</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>124.1553075798997</v>
+        <v>99.32424606391974</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2344806579027041</v>
+        <v>0.2338230791021787</v>
       </c>
       <c r="C7">
-        <v>12.14295854018794</v>
+        <v>12.06185590610828</v>
       </c>
       <c r="D7">
-        <v>12.63745854018794</v>
+        <v>12.68165590610828</v>
       </c>
       <c r="E7">
-        <v>-3.4335</v>
+        <v>-3.308199999999999</v>
       </c>
       <c r="F7">
-        <v>0.6265000000000001</v>
+        <v>0.7518000000000001</v>
       </c>
       <c r="G7">
         <v>0.132</v>
@@ -1849,28 +1849,28 @@
         <v>3.13</v>
       </c>
       <c r="M7">
-        <v>0.03151295</v>
+        <v>0.03781554</v>
       </c>
       <c r="N7">
-        <v>3.09848705</v>
+        <v>3.09218446</v>
       </c>
       <c r="O7">
-        <v>0.8985612444999999</v>
+        <v>0.8967334933999999</v>
       </c>
       <c r="P7">
-        <v>2.1999258055</v>
+        <v>2.1954509666</v>
       </c>
       <c r="Q7">
-        <v>2.9199258055</v>
+        <v>2.9154509666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2449421135817939</v>
+        <v>0.2464684033001901</v>
       </c>
       <c r="T7">
-        <v>1.217928376515726</v>
+        <v>1.227262974433688</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>99.32424606391974</v>
+        <v>82.77020505326645</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2338230791021787</v>
+        <v>0.2331655003016533</v>
       </c>
       <c r="C8">
-        <v>12.06185590610828</v>
+        <v>11.98106350257609</v>
       </c>
       <c r="D8">
-        <v>12.68165590610828</v>
+        <v>12.72616350257609</v>
       </c>
       <c r="E8">
-        <v>-3.308199999999999</v>
+        <v>-3.1829</v>
       </c>
       <c r="F8">
-        <v>0.7518</v>
+        <v>0.8771</v>
       </c>
       <c r="G8">
         <v>0.132</v>
@@ -1931,28 +1931,28 @@
         <v>3.13</v>
       </c>
       <c r="M8">
-        <v>0.03781554</v>
+        <v>0.04411813</v>
       </c>
       <c r="N8">
-        <v>3.09218446</v>
+        <v>3.08588187</v>
       </c>
       <c r="O8">
-        <v>0.8967334933999999</v>
+        <v>0.8949057422999999</v>
       </c>
       <c r="P8">
-        <v>2.1954509666</v>
+        <v>2.1909761277</v>
       </c>
       <c r="Q8">
-        <v>2.9154509666</v>
+        <v>2.9109761277</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2464684033001901</v>
+        <v>0.2480275164533906</v>
       </c>
       <c r="T8">
-        <v>1.227262974433688</v>
+        <v>1.236798316392895</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>82.77020505326645</v>
+        <v>70.94589004565697</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2331655003016532</v>
+        <v>0.2325079215011278</v>
       </c>
       <c r="C9">
-        <v>11.98106350257609</v>
+        <v>11.90058460745494</v>
       </c>
       <c r="D9">
-        <v>12.72616350257609</v>
+        <v>12.77098460745494</v>
       </c>
       <c r="E9">
-        <v>-3.182899999999999</v>
+        <v>-3.057599999999999</v>
       </c>
       <c r="F9">
-        <v>0.8771000000000002</v>
+        <v>1.0024</v>
       </c>
       <c r="G9">
         <v>0.132</v>
@@ -2013,28 +2013,28 @@
         <v>3.13</v>
       </c>
       <c r="M9">
-        <v>0.04411813000000001</v>
+        <v>0.05042072000000001</v>
       </c>
       <c r="N9">
-        <v>3.08588187</v>
+        <v>3.07957928</v>
       </c>
       <c r="O9">
-        <v>0.8949057422999999</v>
+        <v>0.8930779911999999</v>
       </c>
       <c r="P9">
-        <v>2.1909761277</v>
+        <v>2.1865012888</v>
       </c>
       <c r="Q9">
-        <v>2.9109761277</v>
+        <v>2.9065012888</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2480275164533906</v>
+        <v>0.2496205233707911</v>
       </c>
       <c r="T9">
-        <v>1.236798316392895</v>
+        <v>1.246540948394694</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>70.94589004565695</v>
+        <v>62.07765378994984</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2325079215011278</v>
+        <v>0.2318503427006023</v>
       </c>
       <c r="C10">
-        <v>11.90058460745494</v>
+        <v>11.8204225449497</v>
       </c>
       <c r="D10">
-        <v>12.77098460745494</v>
+        <v>12.8161225449497</v>
       </c>
       <c r="E10">
-        <v>-3.057599999999999</v>
+        <v>-2.9323</v>
       </c>
       <c r="F10">
-        <v>1.0024</v>
+        <v>1.1277</v>
       </c>
       <c r="G10">
         <v>0.132</v>
@@ -2095,28 +2095,28 @@
         <v>3.13</v>
       </c>
       <c r="M10">
-        <v>0.05042072000000001</v>
+        <v>0.05672331000000001</v>
       </c>
       <c r="N10">
-        <v>3.07957928</v>
+        <v>3.07327669</v>
       </c>
       <c r="O10">
-        <v>0.8930779911999999</v>
+        <v>0.8912502400999999</v>
       </c>
       <c r="P10">
-        <v>2.1865012888</v>
+        <v>2.1820264499</v>
       </c>
       <c r="Q10">
-        <v>2.9065012888</v>
+        <v>2.9020264499</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2496205233707911</v>
+        <v>0.2512485414292333</v>
       </c>
       <c r="T10">
-        <v>1.246540948394694</v>
+        <v>1.256497704176753</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>62.07765378994984</v>
+        <v>55.18013670217763</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2318503427006023</v>
+        <v>0.2311927639000768</v>
       </c>
       <c r="C11">
-        <v>11.8204225449497</v>
+        <v>11.7405806864284</v>
       </c>
       <c r="D11">
-        <v>12.8161225449497</v>
+        <v>12.8615806864284</v>
       </c>
       <c r="E11">
-        <v>-2.9323</v>
+        <v>-2.806999999999999</v>
       </c>
       <c r="F11">
-        <v>1.1277</v>
+        <v>1.253</v>
       </c>
       <c r="G11">
         <v>0.132</v>
@@ -2177,28 +2177,28 @@
         <v>3.13</v>
       </c>
       <c r="M11">
-        <v>0.05672331000000001</v>
+        <v>0.0630259</v>
       </c>
       <c r="N11">
-        <v>3.07327669</v>
+        <v>3.0669741</v>
       </c>
       <c r="O11">
-        <v>0.8912502400999999</v>
+        <v>0.8894224889999999</v>
       </c>
       <c r="P11">
-        <v>2.1820264499</v>
+        <v>2.177551611</v>
       </c>
       <c r="Q11">
-        <v>2.9020264499</v>
+        <v>2.897551611</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2512485414292333</v>
+        <v>0.252912737666752</v>
       </c>
       <c r="T11">
-        <v>1.256497704176753</v>
+        <v>1.266675721198412</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.18013670217763</v>
+        <v>49.66212303195988</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2311927639000768</v>
+        <v>0.2305351850995514</v>
       </c>
       <c r="C12">
-        <v>11.7405806864284</v>
+        <v>11.66106245126158</v>
       </c>
       <c r="D12">
-        <v>12.8615806864284</v>
+        <v>12.90736245126158</v>
       </c>
       <c r="E12">
-        <v>-2.806999999999999</v>
+        <v>-2.681699999999999</v>
       </c>
       <c r="F12">
-        <v>1.253</v>
+        <v>1.3783</v>
       </c>
       <c r="G12">
         <v>0.132</v>
@@ -2259,28 +2259,28 @@
         <v>3.13</v>
       </c>
       <c r="M12">
-        <v>0.0630259</v>
+        <v>0.06932849000000001</v>
       </c>
       <c r="N12">
-        <v>3.0669741</v>
+        <v>3.06067151</v>
       </c>
       <c r="O12">
-        <v>0.8894224889999999</v>
+        <v>0.8875947378999999</v>
       </c>
       <c r="P12">
-        <v>2.177551611</v>
+        <v>2.1730767721</v>
       </c>
       <c r="Q12">
-        <v>2.897551611</v>
+        <v>2.8930767721</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.252912737666752</v>
+        <v>0.2546143315725297</v>
       </c>
       <c r="T12">
-        <v>1.266675721198412</v>
+        <v>1.277082457703705</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.66212303195988</v>
+        <v>45.14738457450897</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2305351850995514</v>
+        <v>0.2298776062990259</v>
       </c>
       <c r="C13">
-        <v>11.66106245126158</v>
+        <v>11.58187130767979</v>
       </c>
       <c r="D13">
-        <v>12.90736245126158</v>
+        <v>12.95347130767979</v>
       </c>
       <c r="E13">
-        <v>-2.681699999999999</v>
+        <v>-2.5564</v>
       </c>
       <c r="F13">
-        <v>1.3783</v>
+        <v>1.5036</v>
       </c>
       <c r="G13">
         <v>0.132</v>
@@ -2341,28 +2341,28 @@
         <v>3.13</v>
       </c>
       <c r="M13">
-        <v>0.06932849000000001</v>
+        <v>0.07563108</v>
       </c>
       <c r="N13">
-        <v>3.06067151</v>
+        <v>3.05436892</v>
       </c>
       <c r="O13">
-        <v>0.8875947378999999</v>
+        <v>0.8857669867999999</v>
       </c>
       <c r="P13">
-        <v>2.1730767721</v>
+        <v>2.1686019332</v>
       </c>
       <c r="Q13">
-        <v>2.8930767721</v>
+        <v>2.8886019332</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2546143315725297</v>
+        <v>0.2563545980670749</v>
       </c>
       <c r="T13">
-        <v>1.277082457703705</v>
+        <v>1.287725710947754</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.14738457450897</v>
+        <v>41.38510252663323</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2298776062990259</v>
+        <v>0.2292200274985005</v>
       </c>
       <c r="C14">
-        <v>11.58187130767979</v>
+        <v>11.50301077364931</v>
       </c>
       <c r="D14">
-        <v>12.95347130767979</v>
+        <v>12.99991077364931</v>
       </c>
       <c r="E14">
-        <v>-2.5564</v>
+        <v>-2.431099999999999</v>
       </c>
       <c r="F14">
-        <v>1.5036</v>
+        <v>1.6289</v>
       </c>
       <c r="G14">
         <v>0.132</v>
@@ -2423,28 +2423,28 @@
         <v>3.13</v>
       </c>
       <c r="M14">
-        <v>0.07563108</v>
+        <v>0.08193367000000001</v>
       </c>
       <c r="N14">
-        <v>3.05436892</v>
+        <v>3.04806633</v>
       </c>
       <c r="O14">
-        <v>0.8857669867999999</v>
+        <v>0.8839392356999999</v>
       </c>
       <c r="P14">
-        <v>2.1686019332</v>
+        <v>2.1641270943</v>
       </c>
       <c r="Q14">
-        <v>2.8886019332</v>
+        <v>2.8841270943</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2563545980670749</v>
+        <v>0.2581348706879316</v>
       </c>
       <c r="T14">
-        <v>1.287725710947754</v>
+        <v>1.298613636680172</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.38510252663323</v>
+        <v>38.20163310150759</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2292200274985005</v>
+        <v>0.228562448697975</v>
       </c>
       <c r="C15">
-        <v>11.50301077364931</v>
+        <v>11.42448441776698</v>
       </c>
       <c r="D15">
-        <v>12.99991077364931</v>
+        <v>13.04668441776698</v>
       </c>
       <c r="E15">
-        <v>-2.431099999999999</v>
+        <v>-2.305799999999999</v>
       </c>
       <c r="F15">
-        <v>1.6289</v>
+        <v>1.7542</v>
       </c>
       <c r="G15">
         <v>0.132</v>
@@ -2505,28 +2505,28 @@
         <v>3.13</v>
       </c>
       <c r="M15">
-        <v>0.08193367000000001</v>
+        <v>0.08823626000000001</v>
       </c>
       <c r="N15">
-        <v>3.04806633</v>
+        <v>3.04176374</v>
       </c>
       <c r="O15">
-        <v>0.8839392356999999</v>
+        <v>0.8821114845999999</v>
       </c>
       <c r="P15">
-        <v>2.1641270943</v>
+        <v>2.1596522554</v>
       </c>
       <c r="Q15">
-        <v>2.8841270943</v>
+        <v>2.8796522554</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2581348706879316</v>
+        <v>0.2599565449976454</v>
       </c>
       <c r="T15">
-        <v>1.298613636680172</v>
+        <v>1.309754769987763</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.20163310150759</v>
+        <v>35.47294502282848</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.228562448697975</v>
+        <v>0.2279048698974495</v>
       </c>
       <c r="C16">
-        <v>11.42448441776698</v>
+        <v>11.34629586017432</v>
       </c>
       <c r="D16">
-        <v>13.04668441776698</v>
+        <v>13.09379586017432</v>
       </c>
       <c r="E16">
-        <v>-2.305799999999999</v>
+        <v>-2.180499999999999</v>
       </c>
       <c r="F16">
-        <v>1.7542</v>
+        <v>1.8795</v>
       </c>
       <c r="G16">
         <v>0.132</v>
@@ -2587,28 +2587,28 @@
         <v>3.13</v>
       </c>
       <c r="M16">
-        <v>0.08823626000000001</v>
+        <v>0.09453885000000002</v>
       </c>
       <c r="N16">
-        <v>3.04176374</v>
+        <v>3.03546115</v>
       </c>
       <c r="O16">
-        <v>0.8821114845999999</v>
+        <v>0.8802837334999999</v>
       </c>
       <c r="P16">
-        <v>2.1596522554</v>
+        <v>2.1551774165</v>
       </c>
       <c r="Q16">
-        <v>2.8796522554</v>
+        <v>2.8751774165</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2599565449976454</v>
+        <v>0.2618210822322936</v>
       </c>
       <c r="T16">
-        <v>1.309754769987763</v>
+        <v>1.321158047608473</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.47294502282848</v>
+        <v>33.10808202130657</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2279048698974495</v>
+        <v>0.2272472910969241</v>
       </c>
       <c r="C17">
-        <v>11.34629586017432</v>
+        <v>11.2684487734915</v>
       </c>
       <c r="D17">
-        <v>13.09379586017432</v>
+        <v>13.1412487734915</v>
       </c>
       <c r="E17">
-        <v>-2.180499999999999</v>
+        <v>-2.055199999999999</v>
       </c>
       <c r="F17">
-        <v>1.8795</v>
+        <v>2.0048</v>
       </c>
       <c r="G17">
         <v>0.132</v>
@@ -2669,28 +2669,28 @@
         <v>3.13</v>
       </c>
       <c r="M17">
-        <v>0.09453885000000001</v>
+        <v>0.10084144</v>
       </c>
       <c r="N17">
-        <v>3.03546115</v>
+        <v>3.02915856</v>
       </c>
       <c r="O17">
-        <v>0.8802837334999999</v>
+        <v>0.8784559823999999</v>
       </c>
       <c r="P17">
-        <v>2.1551774165</v>
+        <v>2.1507025776</v>
       </c>
       <c r="Q17">
-        <v>2.8751774165</v>
+        <v>2.8707025776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2618210822322936</v>
+        <v>0.2637300132106239</v>
       </c>
       <c r="T17">
-        <v>1.321158047608473</v>
+        <v>1.3328328318392</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.10808202130658</v>
+        <v>31.03882689497492</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2272472910969241</v>
+        <v>0.2265897122963986</v>
       </c>
       <c r="C18">
-        <v>11.2684487734915</v>
+        <v>11.19094688377176</v>
       </c>
       <c r="D18">
-        <v>13.1412487734915</v>
+        <v>13.18904688377176</v>
       </c>
       <c r="E18">
-        <v>-2.055199999999999</v>
+        <v>-1.929899999999999</v>
       </c>
       <c r="F18">
-        <v>2.0048</v>
+        <v>2.130100000000001</v>
       </c>
       <c r="G18">
         <v>0.132</v>
@@ -2751,28 +2751,28 @@
         <v>3.13</v>
       </c>
       <c r="M18">
-        <v>0.10084144</v>
+        <v>0.10714403</v>
       </c>
       <c r="N18">
-        <v>3.02915856</v>
+        <v>3.02285597</v>
       </c>
       <c r="O18">
-        <v>0.8784559823999999</v>
+        <v>0.8766282312999999</v>
       </c>
       <c r="P18">
-        <v>2.1507025776</v>
+        <v>2.1462277387</v>
       </c>
       <c r="Q18">
-        <v>2.8707025776</v>
+        <v>2.8662277387</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2637300132106239</v>
+        <v>0.2656849425257815</v>
       </c>
       <c r="T18">
-        <v>1.3328328318392</v>
+        <v>1.344788936171873</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.03882689497492</v>
+        <v>29.21301354821168</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2265897122963986</v>
+        <v>0.2259321334958732</v>
       </c>
       <c r="C19">
-        <v>11.19094688377176</v>
+        <v>11.1137939714767</v>
       </c>
       <c r="D19">
-        <v>13.18904688377176</v>
+        <v>13.2371939714767</v>
       </c>
       <c r="E19">
-        <v>-1.929899999999999</v>
+        <v>-1.804599999999999</v>
       </c>
       <c r="F19">
-        <v>2.130100000000001</v>
+        <v>2.2554</v>
       </c>
       <c r="G19">
         <v>0.132</v>
@@ -2833,28 +2833,28 @@
         <v>3.13</v>
       </c>
       <c r="M19">
-        <v>0.10714403</v>
+        <v>0.11344662</v>
       </c>
       <c r="N19">
-        <v>3.02285597</v>
+        <v>3.01655338</v>
       </c>
       <c r="O19">
-        <v>0.8766282312999999</v>
+        <v>0.8748004801999999</v>
       </c>
       <c r="P19">
-        <v>2.1462277387</v>
+        <v>2.1417528998</v>
       </c>
       <c r="Q19">
-        <v>2.8662277387</v>
+        <v>2.8617528998</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2656849425257815</v>
+        <v>0.2676875530437478</v>
       </c>
       <c r="T19">
-        <v>1.344788936171873</v>
+        <v>1.357036652805342</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.21301354821168</v>
+        <v>27.59006835108882</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2259321334958732</v>
+        <v>0.2252745546953477</v>
       </c>
       <c r="C20">
-        <v>11.1137939714767</v>
+        <v>11.03699387247304</v>
       </c>
       <c r="D20">
-        <v>13.2371939714767</v>
+        <v>13.28569387247304</v>
       </c>
       <c r="E20">
-        <v>-1.804599999999999</v>
+        <v>-1.6793</v>
       </c>
       <c r="F20">
-        <v>2.2554</v>
+        <v>2.3807</v>
       </c>
       <c r="G20">
         <v>0.132</v>
@@ -2915,28 +2915,28 @@
         <v>3.13</v>
       </c>
       <c r="M20">
-        <v>0.11344662</v>
+        <v>0.11974921</v>
       </c>
       <c r="N20">
-        <v>3.01655338</v>
+        <v>3.01025079</v>
       </c>
       <c r="O20">
-        <v>0.8748004801999999</v>
+        <v>0.8729727290999999</v>
       </c>
       <c r="P20">
-        <v>2.1417528998</v>
+        <v>2.1372780609</v>
       </c>
       <c r="Q20">
-        <v>2.8617528998</v>
+        <v>2.8572780609</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2676875530437478</v>
+        <v>0.2697396107349971</v>
       </c>
       <c r="T20">
-        <v>1.357036652805342</v>
+        <v>1.369586782195194</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.59006835108882</v>
+        <v>26.1379594905052</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2252745546953477</v>
+        <v>0.2246169758948222</v>
       </c>
       <c r="C21">
-        <v>11.03699387247304</v>
+        <v>10.96055047905131</v>
       </c>
       <c r="D21">
-        <v>13.28569387247304</v>
+        <v>13.33455047905131</v>
       </c>
       <c r="E21">
-        <v>-1.6793</v>
+        <v>-1.553999999999999</v>
       </c>
       <c r="F21">
-        <v>2.3807</v>
+        <v>2.506</v>
       </c>
       <c r="G21">
         <v>0.132</v>
@@ -2997,28 +2997,28 @@
         <v>3.13</v>
       </c>
       <c r="M21">
-        <v>0.11974921</v>
+        <v>0.1260518</v>
       </c>
       <c r="N21">
-        <v>3.01025079</v>
+        <v>3.0039482</v>
       </c>
       <c r="O21">
-        <v>0.8729727290999999</v>
+        <v>0.8711449779999999</v>
       </c>
       <c r="P21">
-        <v>2.1372780609</v>
+        <v>2.132803222</v>
       </c>
       <c r="Q21">
-        <v>2.8572780609</v>
+        <v>2.852803222</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2697396107349971</v>
+        <v>0.2718429698685278</v>
       </c>
       <c r="T21">
-        <v>1.369586782195194</v>
+        <v>1.382450664819791</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.1379594905052</v>
+        <v>24.83106151597994</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2246169758948222</v>
+        <v>0.2239593970942968</v>
       </c>
       <c r="C22">
-        <v>10.96055047905131</v>
+        <v>10.88446774096716</v>
       </c>
       <c r="D22">
-        <v>13.33455047905131</v>
+        <v>13.38376774096716</v>
       </c>
       <c r="E22">
-        <v>-1.553999999999999</v>
+        <v>-1.428699999999999</v>
       </c>
       <c r="F22">
-        <v>2.506</v>
+        <v>2.6313</v>
       </c>
       <c r="G22">
         <v>0.132</v>
@@ -3079,28 +3079,28 @@
         <v>3.13</v>
       </c>
       <c r="M22">
-        <v>0.1260518</v>
+        <v>0.13235439</v>
       </c>
       <c r="N22">
-        <v>3.0039482</v>
+        <v>2.99764561</v>
       </c>
       <c r="O22">
-        <v>0.8711449779999999</v>
+        <v>0.8693172268999999</v>
       </c>
       <c r="P22">
-        <v>2.132803222</v>
+        <v>2.1283283831</v>
       </c>
       <c r="Q22">
-        <v>2.852803222</v>
+        <v>2.8483283831</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2718429698685278</v>
+        <v>0.2739995786003757</v>
       </c>
       <c r="T22">
-        <v>1.382450664819791</v>
+        <v>1.395640215358936</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.83106151597994</v>
+        <v>23.64863001521898</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2239593970942968</v>
+        <v>0.2233018182937713</v>
       </c>
       <c r="C23">
-        <v>10.88446774096716</v>
+        <v>10.80874966650581</v>
       </c>
       <c r="D23">
-        <v>13.38376774096716</v>
+        <v>13.43334966650581</v>
       </c>
       <c r="E23">
-        <v>-1.4287</v>
+        <v>-1.303399999999999</v>
       </c>
       <c r="F23">
-        <v>2.6313</v>
+        <v>2.7566</v>
       </c>
       <c r="G23">
         <v>0.132</v>
@@ -3161,28 +3161,28 @@
         <v>3.13</v>
       </c>
       <c r="M23">
-        <v>0.13235439</v>
+        <v>0.13865698</v>
       </c>
       <c r="N23">
-        <v>2.99764561</v>
+        <v>2.99134302</v>
       </c>
       <c r="O23">
-        <v>0.8693172268999999</v>
+        <v>0.8674894757999999</v>
       </c>
       <c r="P23">
-        <v>2.1283283831</v>
+        <v>2.1238535442</v>
       </c>
       <c r="Q23">
-        <v>2.8483283831</v>
+        <v>2.8438535442</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2739995786003757</v>
+        <v>0.2762114849920145</v>
       </c>
       <c r="T23">
-        <v>1.395640215358936</v>
+        <v>1.409167959501648</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.64863001521899</v>
+        <v>22.57369228725449</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2233018182937713</v>
+        <v>0.2226442394932459</v>
       </c>
       <c r="C24">
-        <v>10.80874966650581</v>
+        <v>10.7334003235702</v>
       </c>
       <c r="D24">
-        <v>13.43334966650581</v>
+        <v>13.4833003235702</v>
       </c>
       <c r="E24">
-        <v>-1.303399999999999</v>
+        <v>-1.178099999999999</v>
       </c>
       <c r="F24">
-        <v>2.7566</v>
+        <v>2.8819</v>
       </c>
       <c r="G24">
         <v>0.132</v>
@@ -3243,28 +3243,28 @@
         <v>3.13</v>
       </c>
       <c r="M24">
-        <v>0.13865698</v>
+        <v>0.14495957</v>
       </c>
       <c r="N24">
-        <v>2.99134302</v>
+        <v>2.98504043</v>
       </c>
       <c r="O24">
-        <v>0.8674894757999999</v>
+        <v>0.8656617246999999</v>
       </c>
       <c r="P24">
-        <v>2.1238535442</v>
+        <v>2.1193787053</v>
       </c>
       <c r="Q24">
-        <v>2.8438535442</v>
+        <v>2.8393787053</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2762114849920145</v>
+        <v>0.2784808434977219</v>
       </c>
       <c r="T24">
-        <v>1.409167959501648</v>
+        <v>1.423047073622093</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.57369228725449</v>
+        <v>21.59222740519994</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2226442394932459</v>
+        <v>0.2219866606927204</v>
       </c>
       <c r="C25">
-        <v>10.7334003235702</v>
+        <v>10.65842384079357</v>
       </c>
       <c r="D25">
-        <v>13.4833003235702</v>
+        <v>13.53362384079357</v>
       </c>
       <c r="E25">
-        <v>-1.178099999999999</v>
+        <v>-1.052799999999999</v>
       </c>
       <c r="F25">
-        <v>2.8819</v>
+        <v>3.007200000000001</v>
       </c>
       <c r="G25">
         <v>0.132</v>
@@ -3325,28 +3325,28 @@
         <v>3.13</v>
       </c>
       <c r="M25">
-        <v>0.14495957</v>
+        <v>0.15126216</v>
       </c>
       <c r="N25">
-        <v>2.98504043</v>
+        <v>2.97873784</v>
       </c>
       <c r="O25">
-        <v>0.8656617246999999</v>
+        <v>0.8638339735999999</v>
       </c>
       <c r="P25">
-        <v>2.1193787053</v>
+        <v>2.1149038664</v>
       </c>
       <c r="Q25">
-        <v>2.8393787053</v>
+        <v>2.8349038664</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2784808434977219</v>
+        <v>0.2808099219641058</v>
       </c>
       <c r="T25">
-        <v>1.423047073622093</v>
+        <v>1.437291427587813</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.59222740519994</v>
+        <v>20.69255126331661</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2219866606927204</v>
+        <v>0.2213290818921949</v>
       </c>
       <c r="C26">
-        <v>10.65842384079357</v>
+        <v>10.583824408677</v>
       </c>
       <c r="D26">
-        <v>13.53362384079357</v>
+        <v>13.584324408677</v>
       </c>
       <c r="E26">
-        <v>-1.0528</v>
+        <v>-0.9274999999999993</v>
       </c>
       <c r="F26">
-        <v>3.0072</v>
+        <v>3.1325</v>
       </c>
       <c r="G26">
         <v>0.132</v>
@@ -3407,28 +3407,28 @@
         <v>3.13</v>
       </c>
       <c r="M26">
-        <v>0.15126216</v>
+        <v>0.15756475</v>
       </c>
       <c r="N26">
-        <v>2.97873784</v>
+        <v>2.97243525</v>
       </c>
       <c r="O26">
-        <v>0.8638339735999999</v>
+        <v>0.8620062224999999</v>
       </c>
       <c r="P26">
-        <v>2.1149038664</v>
+        <v>2.1104290275</v>
       </c>
       <c r="Q26">
-        <v>2.8349038664</v>
+        <v>2.8304290275</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2808099219641058</v>
+        <v>0.2832011091895932</v>
       </c>
       <c r="T26">
-        <v>1.437291427587813</v>
+        <v>1.451915630992619</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.69255126331661</v>
+        <v>19.86484921278395</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2213290818921949</v>
+        <v>0.2206715030916695</v>
       </c>
       <c r="C27">
-        <v>10.583824408677</v>
+        <v>10.50960628075266</v>
       </c>
       <c r="D27">
-        <v>13.584324408677</v>
+        <v>13.63540628075266</v>
       </c>
       <c r="E27">
-        <v>-0.9274999999999993</v>
+        <v>-0.8021999999999991</v>
       </c>
       <c r="F27">
-        <v>3.1325</v>
+        <v>3.2578</v>
       </c>
       <c r="G27">
         <v>0.132</v>
@@ -3489,28 +3489,28 @@
         <v>3.13</v>
       </c>
       <c r="M27">
-        <v>0.15756475</v>
+        <v>0.16386734</v>
       </c>
       <c r="N27">
-        <v>2.97243525</v>
+        <v>2.96613266</v>
       </c>
       <c r="O27">
-        <v>0.8620062224999999</v>
+        <v>0.8601784713999999</v>
       </c>
       <c r="P27">
-        <v>2.1104290275</v>
+        <v>2.1059541886</v>
       </c>
       <c r="Q27">
-        <v>2.8304290275</v>
+        <v>2.8259541886</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2832011091895932</v>
+        <v>0.2856569230968506</v>
       </c>
       <c r="T27">
-        <v>1.451915630992619</v>
+        <v>1.466935083138095</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.86484921278395</v>
+        <v>19.10081655075379</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2206715030916695</v>
+        <v>0.220013924291144</v>
       </c>
       <c r="C28">
-        <v>10.50960628075266</v>
+        <v>10.43577377477335</v>
       </c>
       <c r="D28">
-        <v>13.63540628075266</v>
+        <v>13.68687377477335</v>
       </c>
       <c r="E28">
-        <v>-0.8021999999999991</v>
+        <v>-0.6768999999999989</v>
       </c>
       <c r="F28">
-        <v>3.2578</v>
+        <v>3.383100000000001</v>
       </c>
       <c r="G28">
         <v>0.132</v>
@@ -3571,28 +3571,28 @@
         <v>3.13</v>
       </c>
       <c r="M28">
-        <v>0.16386734</v>
+        <v>0.17016993</v>
       </c>
       <c r="N28">
-        <v>2.96613266</v>
+        <v>2.95983007</v>
       </c>
       <c r="O28">
-        <v>0.8601784713999999</v>
+        <v>0.8583507202999999</v>
       </c>
       <c r="P28">
-        <v>2.1059541886</v>
+        <v>2.1014793497</v>
       </c>
       <c r="Q28">
-        <v>2.8259541886</v>
+        <v>2.8214793497</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2856569230968506</v>
+        <v>0.2881800195769096</v>
       </c>
       <c r="T28">
-        <v>1.466935083138095</v>
+        <v>1.482366027123173</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.10081655075379</v>
+        <v>18.39337890072588</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.220013924291144</v>
+        <v>0.2193563454906186</v>
       </c>
       <c r="C29">
-        <v>10.43577377477335</v>
+        <v>10.36233127392912</v>
       </c>
       <c r="D29">
-        <v>13.68687377477335</v>
+        <v>13.73873127392912</v>
       </c>
       <c r="E29">
-        <v>-0.6768999999999989</v>
+        <v>-0.5515999999999988</v>
       </c>
       <c r="F29">
-        <v>3.383100000000001</v>
+        <v>3.508400000000001</v>
       </c>
       <c r="G29">
         <v>0.132</v>
@@ -3653,28 +3653,28 @@
         <v>3.13</v>
       </c>
       <c r="M29">
-        <v>0.17016993</v>
+        <v>0.17647252</v>
       </c>
       <c r="N29">
-        <v>2.95983007</v>
+        <v>2.95352748</v>
       </c>
       <c r="O29">
-        <v>0.8583507202999999</v>
+        <v>0.8565229691999999</v>
       </c>
       <c r="P29">
-        <v>2.1014793497</v>
+        <v>2.0970045108</v>
       </c>
       <c r="Q29">
-        <v>2.8214793497</v>
+        <v>2.8170045108</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2881800195769096</v>
+        <v>0.2907732020703035</v>
       </c>
       <c r="T29">
-        <v>1.482366027123173</v>
+        <v>1.498225608441171</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.39337890072588</v>
+        <v>17.73647251141424</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2193563454906186</v>
+        <v>0.2186987666900931</v>
       </c>
       <c r="C30">
-        <v>10.36233127392912</v>
+        <v>10.28928322809167</v>
       </c>
       <c r="D30">
-        <v>13.73873127392912</v>
+        <v>13.79098322809167</v>
       </c>
       <c r="E30">
-        <v>-0.5515999999999988</v>
+        <v>-0.426299999999999</v>
       </c>
       <c r="F30">
-        <v>3.508400000000001</v>
+        <v>3.633700000000001</v>
       </c>
       <c r="G30">
         <v>0.132</v>
@@ -3735,28 +3735,28 @@
         <v>3.13</v>
       </c>
       <c r="M30">
-        <v>0.17647252</v>
+        <v>0.18277511</v>
       </c>
       <c r="N30">
-        <v>2.95352748</v>
+        <v>2.94722489</v>
       </c>
       <c r="O30">
-        <v>0.8565229691999999</v>
+        <v>0.8546952180999998</v>
       </c>
       <c r="P30">
-        <v>2.0970045108</v>
+        <v>2.0925296719</v>
       </c>
       <c r="Q30">
-        <v>2.8170045108</v>
+        <v>2.8125296719</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2907732020703035</v>
+        <v>0.2934394319578776</v>
       </c>
       <c r="T30">
-        <v>1.498225608441171</v>
+        <v>1.514531938528689</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.73647251141424</v>
+        <v>17.12487001102064</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2186987666900931</v>
+        <v>0.2180411878895676</v>
       </c>
       <c r="C31">
-        <v>10.28928322809167</v>
+        <v>10.21663415508719</v>
       </c>
       <c r="D31">
-        <v>13.79098322809167</v>
+        <v>13.84363415508719</v>
       </c>
       <c r="E31">
-        <v>-0.4262999999999995</v>
+        <v>-0.3009999999999993</v>
       </c>
       <c r="F31">
-        <v>3.6337</v>
+        <v>3.759</v>
       </c>
       <c r="G31">
         <v>0.132</v>
@@ -3817,28 +3817,28 @@
         <v>3.13</v>
       </c>
       <c r="M31">
-        <v>0.18277511</v>
+        <v>0.1890777</v>
       </c>
       <c r="N31">
-        <v>2.94722489</v>
+        <v>2.9409223</v>
       </c>
       <c r="O31">
-        <v>0.8546952180999998</v>
+        <v>0.8528674669999999</v>
       </c>
       <c r="P31">
-        <v>2.0925296719</v>
+        <v>2.088054833</v>
       </c>
       <c r="Q31">
-        <v>2.8125296719</v>
+        <v>2.808054833</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2934394319578776</v>
+        <v>0.2961818398422394</v>
       </c>
       <c r="T31">
-        <v>1.514531938528689</v>
+        <v>1.531304163761565</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.12487001102065</v>
+        <v>16.55404101065329</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2180411878895676</v>
+        <v>0.2173836090890421</v>
       </c>
       <c r="C32">
-        <v>10.21663415508719</v>
+        <v>10.14438864199853</v>
       </c>
       <c r="D32">
-        <v>13.84363415508719</v>
+        <v>13.89668864199853</v>
       </c>
       <c r="E32">
-        <v>-0.3009999999999993</v>
+        <v>-0.1756999999999991</v>
       </c>
       <c r="F32">
-        <v>3.759</v>
+        <v>3.884300000000001</v>
       </c>
       <c r="G32">
         <v>0.132</v>
@@ -3899,28 +3899,28 @@
         <v>3.13</v>
       </c>
       <c r="M32">
-        <v>0.1890777</v>
+        <v>0.19538029</v>
       </c>
       <c r="N32">
-        <v>2.9409223</v>
+        <v>2.93461971</v>
       </c>
       <c r="O32">
-        <v>0.8528674669999999</v>
+        <v>0.8510397158999998</v>
       </c>
       <c r="P32">
-        <v>2.088054833</v>
+        <v>2.0835799941</v>
       </c>
       <c r="Q32">
-        <v>2.808054833</v>
+        <v>2.8035799941</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2961818398422394</v>
+        <v>0.299003737810206</v>
       </c>
       <c r="T32">
-        <v>1.531304163761565</v>
+        <v>1.548562540450466</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.55404101065329</v>
+        <v>16.02003968772899</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2173836090890421</v>
+        <v>0.2167260302885167</v>
       </c>
       <c r="C33">
-        <v>10.14438864199853</v>
+        <v>10.07255134649741</v>
       </c>
       <c r="D33">
-        <v>13.89668864199853</v>
+        <v>13.95015134649741</v>
       </c>
       <c r="E33">
-        <v>-0.1756999999999991</v>
+        <v>-0.05039999999999889</v>
       </c>
       <c r="F33">
-        <v>3.884300000000001</v>
+        <v>4.009600000000001</v>
       </c>
       <c r="G33">
         <v>0.132</v>
@@ -3981,28 +3981,28 @@
         <v>3.13</v>
       </c>
       <c r="M33">
-        <v>0.19538029</v>
+        <v>0.20168288</v>
       </c>
       <c r="N33">
-        <v>2.93461971</v>
+        <v>2.92831712</v>
       </c>
       <c r="O33">
-        <v>0.8510397158999998</v>
+        <v>0.8492119647999999</v>
       </c>
       <c r="P33">
-        <v>2.0835799941</v>
+        <v>2.0791051552</v>
       </c>
       <c r="Q33">
-        <v>2.8035799941</v>
+        <v>2.7991051552</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.299003737810206</v>
+        <v>0.3019086327772305</v>
       </c>
       <c r="T33">
-        <v>1.548562540450466</v>
+        <v>1.566328516453747</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.02003968772899</v>
+        <v>15.51941344748746</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2167260302885167</v>
+        <v>0.2160684514879912</v>
       </c>
       <c r="C34">
-        <v>10.07255134649741</v>
+        <v>10.00112699820747</v>
       </c>
       <c r="D34">
-        <v>13.95015134649741</v>
+        <v>14.00402699820747</v>
       </c>
       <c r="E34">
-        <v>-0.05039999999999889</v>
+        <v>0.0749000000000013</v>
       </c>
       <c r="F34">
-        <v>4.009600000000001</v>
+        <v>4.134900000000001</v>
       </c>
       <c r="G34">
         <v>0.132</v>
@@ -4063,28 +4063,28 @@
         <v>3.13</v>
       </c>
       <c r="M34">
-        <v>0.20168288</v>
+        <v>0.20798547</v>
       </c>
       <c r="N34">
-        <v>2.92831712</v>
+        <v>2.92201453</v>
       </c>
       <c r="O34">
-        <v>0.8492119647999999</v>
+        <v>0.8473842136999998</v>
       </c>
       <c r="P34">
-        <v>2.0791051552</v>
+        <v>2.0746303163</v>
       </c>
       <c r="Q34">
-        <v>2.7991051552</v>
+        <v>2.7946303163</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3019086327772305</v>
+        <v>0.3049002410268526</v>
       </c>
       <c r="T34">
-        <v>1.566328516453747</v>
+        <v>1.584624820098916</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.51941344748746</v>
+        <v>15.04912819150299</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2160684514879912</v>
+        <v>0.2154108726874658</v>
       </c>
       <c r="C35">
-        <v>10.00112699820747</v>
+        <v>9.93012040009908</v>
       </c>
       <c r="D35">
-        <v>14.00402699820747</v>
+        <v>14.05832040009908</v>
       </c>
       <c r="E35">
-        <v>0.0749000000000013</v>
+        <v>0.2002000000000015</v>
       </c>
       <c r="F35">
-        <v>4.134900000000001</v>
+        <v>4.260200000000001</v>
       </c>
       <c r="G35">
         <v>0.132</v>
@@ -4145,28 +4145,28 @@
         <v>3.13</v>
       </c>
       <c r="M35">
-        <v>0.20798547</v>
+        <v>0.2142880600000001</v>
       </c>
       <c r="N35">
-        <v>2.92201453</v>
+        <v>2.91571194</v>
       </c>
       <c r="O35">
-        <v>0.8473842136999998</v>
+        <v>0.8455564625999999</v>
       </c>
       <c r="P35">
-        <v>2.0746303163</v>
+        <v>2.0701554774</v>
       </c>
       <c r="Q35">
-        <v>2.7946303163</v>
+        <v>2.7901554774</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3049002410268526</v>
+        <v>0.3079825040719179</v>
       </c>
       <c r="T35">
-        <v>1.584624820098916</v>
+        <v>1.603475557187879</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.04912819150299</v>
+        <v>14.60650677410584</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2154108726874658</v>
+        <v>0.2147532938869403</v>
       </c>
       <c r="C36">
-        <v>9.93012040009908</v>
+        <v>9.859536429916682</v>
       </c>
       <c r="D36">
-        <v>14.05832040009908</v>
+        <v>14.11303642991668</v>
       </c>
       <c r="E36">
-        <v>0.2002000000000015</v>
+        <v>0.3255000000000008</v>
       </c>
       <c r="F36">
-        <v>4.260200000000001</v>
+        <v>4.3855</v>
       </c>
       <c r="G36">
         <v>0.132</v>
@@ -4227,28 +4227,28 @@
         <v>3.13</v>
       </c>
       <c r="M36">
-        <v>0.2142880600000001</v>
+        <v>0.22059065</v>
       </c>
       <c r="N36">
-        <v>2.91571194</v>
+        <v>2.90940935</v>
       </c>
       <c r="O36">
-        <v>0.8455564625999999</v>
+        <v>0.8437287114999998</v>
       </c>
       <c r="P36">
-        <v>2.0701554774</v>
+        <v>2.0656806385</v>
       </c>
       <c r="Q36">
-        <v>2.7901554774</v>
+        <v>2.7856806385</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3079825040719179</v>
+        <v>0.3111596059799082</v>
       </c>
       <c r="T36">
-        <v>1.603475557187879</v>
+        <v>1.622906316956502</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.60650677410584</v>
+        <v>14.18917800913139</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2147532938869403</v>
+        <v>0.2140957150864148</v>
       </c>
       <c r="C37">
-        <v>9.859536429916682</v>
+        <v>9.789380041639607</v>
       </c>
       <c r="D37">
-        <v>14.11303642991668</v>
+        <v>14.16818004163961</v>
       </c>
       <c r="E37">
-        <v>0.3255000000000008</v>
+        <v>0.450800000000001</v>
       </c>
       <c r="F37">
-        <v>4.3855</v>
+        <v>4.510800000000001</v>
       </c>
       <c r="G37">
         <v>0.132</v>
@@ -4309,28 +4309,28 @@
         <v>3.13</v>
       </c>
       <c r="M37">
-        <v>0.22059065</v>
+        <v>0.22689324</v>
       </c>
       <c r="N37">
-        <v>2.90940935</v>
+        <v>2.90310676</v>
       </c>
       <c r="O37">
-        <v>0.8437287114999998</v>
+        <v>0.8419009604</v>
       </c>
       <c r="P37">
-        <v>2.0656806385</v>
+        <v>2.0612057996</v>
       </c>
       <c r="Q37">
-        <v>2.7856806385</v>
+        <v>2.7812057996</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3111596059799082</v>
+        <v>0.3144359923225232</v>
       </c>
       <c r="T37">
-        <v>1.622906316956502</v>
+        <v>1.642944287967895</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.18917800913139</v>
+        <v>13.79503417554441</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2140957150864149</v>
+        <v>0.2134381362858894</v>
       </c>
       <c r="C38">
-        <v>9.789380041639603</v>
+        <v>9.719656266977267</v>
       </c>
       <c r="D38">
-        <v>14.1681800416396</v>
+        <v>14.22375626697727</v>
       </c>
       <c r="E38">
-        <v>0.450800000000001</v>
+        <v>0.5761000000000012</v>
       </c>
       <c r="F38">
-        <v>4.510800000000001</v>
+        <v>4.636100000000001</v>
       </c>
       <c r="G38">
         <v>0.132</v>
@@ -4391,28 +4391,28 @@
         <v>3.13</v>
       </c>
       <c r="M38">
-        <v>0.22689324</v>
+        <v>0.23319583</v>
       </c>
       <c r="N38">
-        <v>2.90310676</v>
+        <v>2.89680417</v>
       </c>
       <c r="O38">
-        <v>0.8419009604</v>
+        <v>0.8400732092999998</v>
       </c>
       <c r="P38">
-        <v>2.0612057996</v>
+        <v>2.0567309607</v>
       </c>
       <c r="Q38">
-        <v>2.7812057996</v>
+        <v>2.7767309607</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3144359923225232</v>
+        <v>0.3178163909299832</v>
       </c>
       <c r="T38">
-        <v>1.642944287967895</v>
+        <v>1.663618385043141</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.79503417554441</v>
+        <v>13.42219541404321</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2134381362858894</v>
+        <v>0.2127805574853639</v>
       </c>
       <c r="C39">
-        <v>9.719656266977267</v>
+        <v>9.650370216899701</v>
       </c>
       <c r="D39">
-        <v>14.22375626697727</v>
+        <v>14.2797702168997</v>
       </c>
       <c r="E39">
-        <v>0.5761000000000012</v>
+        <v>0.7014000000000005</v>
       </c>
       <c r="F39">
-        <v>4.636100000000001</v>
+        <v>4.7614</v>
       </c>
       <c r="G39">
         <v>0.132</v>
@@ -4473,28 +4473,28 @@
         <v>3.13</v>
       </c>
       <c r="M39">
-        <v>0.23319583</v>
+        <v>0.23949842</v>
       </c>
       <c r="N39">
-        <v>2.89680417</v>
+        <v>2.89050158</v>
       </c>
       <c r="O39">
-        <v>0.8400732092999998</v>
+        <v>0.8382454582</v>
       </c>
       <c r="P39">
-        <v>2.0567309607</v>
+        <v>2.0522561218</v>
       </c>
       <c r="Q39">
-        <v>2.7767309607</v>
+        <v>2.7722561218</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3178163909299832</v>
+        <v>0.3213058346538128</v>
       </c>
       <c r="T39">
-        <v>1.663618385043141</v>
+        <v>1.684959388475653</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.42219541404321</v>
+        <v>13.0689797452526</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2127805574853639</v>
+        <v>0.2125383286848385</v>
       </c>
       <c r="C40">
-        <v>9.650370216899701</v>
+        <v>9.545815126835535</v>
       </c>
       <c r="D40">
-        <v>14.2797702168997</v>
+        <v>14.30051512683553</v>
       </c>
       <c r="E40">
-        <v>0.7014000000000005</v>
+        <v>0.8267000000000007</v>
       </c>
       <c r="F40">
-        <v>4.7614</v>
+        <v>4.8867</v>
       </c>
       <c r="G40">
         <v>0.132</v>
@@ -4555,45 +4555,45 @@
         <v>3.13</v>
       </c>
       <c r="M40">
-        <v>0.23949842</v>
+        <v>0.25313106</v>
       </c>
       <c r="N40">
-        <v>2.89050158</v>
+        <v>2.87686894</v>
       </c>
       <c r="O40">
-        <v>0.8382454582</v>
+        <v>0.8342919926</v>
       </c>
       <c r="P40">
-        <v>2.0522561218</v>
+        <v>2.0425769474</v>
       </c>
       <c r="Q40">
-        <v>2.7722561218</v>
+        <v>2.7625769474</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3213058346538128</v>
+        <v>0.3249096863685877</v>
       </c>
       <c r="T40">
-        <v>1.684959388475653</v>
+        <v>1.70700009693874</v>
       </c>
       <c r="U40">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V40">
         <v>0.29</v>
       </c>
       <c r="W40">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y40">
-        <v>13.0689797452526</v>
+        <v>12.3651360682486</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2125383286848385</v>
+        <v>0.211891399884313</v>
       </c>
       <c r="C41">
-        <v>9.545815126835535</v>
+        <v>9.476215874161065</v>
       </c>
       <c r="D41">
-        <v>14.30051512683553</v>
+        <v>14.35621587416107</v>
       </c>
       <c r="E41">
-        <v>0.8267000000000007</v>
+        <v>0.9520000000000008</v>
       </c>
       <c r="F41">
-        <v>4.8867</v>
+        <v>5.012</v>
       </c>
       <c r="G41">
         <v>0.132</v>
@@ -4637,28 +4637,28 @@
         <v>3.13</v>
       </c>
       <c r="M41">
-        <v>0.25313106</v>
+        <v>0.2596216</v>
       </c>
       <c r="N41">
-        <v>2.87686894</v>
+        <v>2.8703784</v>
       </c>
       <c r="O41">
-        <v>0.8342919926</v>
+        <v>0.8324097359999999</v>
       </c>
       <c r="P41">
-        <v>2.0425769474</v>
+        <v>2.037968664</v>
       </c>
       <c r="Q41">
-        <v>2.7625769474</v>
+        <v>2.757968664</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3249096863685877</v>
+        <v>0.3286336664738551</v>
       </c>
       <c r="T41">
-        <v>1.70700009693874</v>
+        <v>1.729775495683929</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.3651360682486</v>
+        <v>12.05600766654238</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.211891399884313</v>
+        <v>0.2112444710837875</v>
       </c>
       <c r="C42">
-        <v>9.476215874161065</v>
+        <v>9.407052228883082</v>
       </c>
       <c r="D42">
-        <v>14.35621587416107</v>
+        <v>14.41235222888308</v>
       </c>
       <c r="E42">
-        <v>0.9520000000000008</v>
+        <v>1.077300000000001</v>
       </c>
       <c r="F42">
-        <v>5.012</v>
+        <v>5.137300000000001</v>
       </c>
       <c r="G42">
         <v>0.132</v>
@@ -4719,28 +4719,28 @@
         <v>3.13</v>
       </c>
       <c r="M42">
-        <v>0.2596216</v>
+        <v>0.2661121400000001</v>
       </c>
       <c r="N42">
-        <v>2.8703784</v>
+        <v>2.86388786</v>
       </c>
       <c r="O42">
-        <v>0.8324097359999999</v>
+        <v>0.8305274793999998</v>
       </c>
       <c r="P42">
-        <v>2.037968664</v>
+        <v>2.0333603806</v>
       </c>
       <c r="Q42">
-        <v>2.757968664</v>
+        <v>2.7533603806</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3286336664738551</v>
+        <v>0.3324838831928603</v>
       </c>
       <c r="T42">
-        <v>1.729775495683929</v>
+        <v>1.753322941844209</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.05600766654238</v>
+        <v>11.76195869906574</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2112444710837875</v>
+        <v>0.2105975422832621</v>
       </c>
       <c r="C43">
-        <v>9.407052228883082</v>
+        <v>9.338329321059344</v>
       </c>
       <c r="D43">
-        <v>14.41235222888308</v>
+        <v>14.46892932105935</v>
       </c>
       <c r="E43">
-        <v>1.077300000000001</v>
+        <v>1.202600000000001</v>
       </c>
       <c r="F43">
-        <v>5.137300000000001</v>
+        <v>5.262600000000001</v>
       </c>
       <c r="G43">
         <v>0.132</v>
@@ -4801,28 +4801,28 @@
         <v>3.13</v>
       </c>
       <c r="M43">
-        <v>0.2661121400000001</v>
+        <v>0.27260268</v>
       </c>
       <c r="N43">
-        <v>2.86388786</v>
+        <v>2.85739732</v>
       </c>
       <c r="O43">
-        <v>0.8305274793999998</v>
+        <v>0.8286452228</v>
       </c>
       <c r="P43">
-        <v>2.0333603806</v>
+        <v>2.0287520972</v>
       </c>
       <c r="Q43">
-        <v>2.7533603806</v>
+        <v>2.7487520972</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3324838831928603</v>
+        <v>0.3364668660056243</v>
       </c>
       <c r="T43">
-        <v>1.753322941844209</v>
+        <v>1.777682368906568</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.76195869906574</v>
+        <v>11.4819120633737</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2105975422832621</v>
+        <v>0.2099506134827366</v>
       </c>
       <c r="C44">
-        <v>9.338329321059341</v>
+        <v>9.270052361619257</v>
       </c>
       <c r="D44">
-        <v>14.46892932105934</v>
+        <v>14.52595236161926</v>
       </c>
       <c r="E44">
-        <v>1.2026</v>
+        <v>1.327900000000001</v>
       </c>
       <c r="F44">
-        <v>5.2626</v>
+        <v>5.3879</v>
       </c>
       <c r="G44">
         <v>0.132</v>
@@ -4883,28 +4883,28 @@
         <v>3.13</v>
       </c>
       <c r="M44">
-        <v>0.27260268</v>
+        <v>0.27909322</v>
       </c>
       <c r="N44">
-        <v>2.85739732</v>
+        <v>2.85090678</v>
       </c>
       <c r="O44">
-        <v>0.8286452228</v>
+        <v>0.8267629661999999</v>
       </c>
       <c r="P44">
-        <v>2.0287520972</v>
+        <v>2.0241438138</v>
       </c>
       <c r="Q44">
-        <v>2.7487520972</v>
+        <v>2.7441438138</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3364668660056243</v>
+        <v>0.3405896026012923</v>
       </c>
       <c r="T44">
-        <v>1.777682368906568</v>
+        <v>1.802896512707958</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.4819120633737</v>
+        <v>11.21489085259757</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2099506134827366</v>
+        <v>0.2093036846822112</v>
       </c>
       <c r="C45">
-        <v>9.270052361619257</v>
+        <v>9.202226643963762</v>
       </c>
       <c r="D45">
-        <v>14.52595236161926</v>
+        <v>14.58342664396376</v>
       </c>
       <c r="E45">
-        <v>1.327900000000001</v>
+        <v>1.453200000000001</v>
       </c>
       <c r="F45">
-        <v>5.3879</v>
+        <v>5.5132</v>
       </c>
       <c r="G45">
         <v>0.132</v>
@@ -4965,28 +4965,28 @@
         <v>3.13</v>
       </c>
       <c r="M45">
-        <v>0.27909322</v>
+        <v>0.28558376</v>
       </c>
       <c r="N45">
-        <v>2.85090678</v>
+        <v>2.84441624</v>
       </c>
       <c r="O45">
-        <v>0.8267629661999999</v>
+        <v>0.8248807095999998</v>
       </c>
       <c r="P45">
-        <v>2.0241438138</v>
+        <v>2.0195355304</v>
       </c>
       <c r="Q45">
-        <v>2.7441438138</v>
+        <v>2.7395355304</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3405896026012923</v>
+        <v>0.3448595797896628</v>
       </c>
       <c r="T45">
-        <v>1.802896512707958</v>
+        <v>1.829011161645111</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.21489085259757</v>
+        <v>10.96000696958398</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2093036846822112</v>
+        <v>0.2086567558816857</v>
       </c>
       <c r="C46">
-        <v>9.202226643963762</v>
+        <v>9.13485754560339</v>
       </c>
       <c r="D46">
-        <v>14.58342664396376</v>
+        <v>14.64135754560339</v>
       </c>
       <c r="E46">
-        <v>1.453200000000001</v>
+        <v>1.578500000000001</v>
       </c>
       <c r="F46">
-        <v>5.5132</v>
+        <v>5.638500000000001</v>
       </c>
       <c r="G46">
         <v>0.132</v>
@@ -5047,28 +5047,28 @@
         <v>3.13</v>
       </c>
       <c r="M46">
-        <v>0.28558376</v>
+        <v>0.2920743</v>
       </c>
       <c r="N46">
-        <v>2.84441624</v>
+        <v>2.8379257</v>
       </c>
       <c r="O46">
-        <v>0.8248807095999998</v>
+        <v>0.822998453</v>
       </c>
       <c r="P46">
-        <v>2.0195355304</v>
+        <v>2.014927247</v>
       </c>
       <c r="Q46">
-        <v>2.7395355304</v>
+        <v>2.734927247</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3448595797896628</v>
+        <v>0.3492848288757922</v>
       </c>
       <c r="T46">
-        <v>1.829011161645111</v>
+        <v>1.856075434179979</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.96000696958398</v>
+        <v>10.71645125914879</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2086567558816857</v>
+        <v>0.2080098270811603</v>
       </c>
       <c r="C47">
-        <v>9.13485754560339</v>
+        <v>9.067950529835485</v>
       </c>
       <c r="D47">
-        <v>14.64135754560339</v>
+        <v>14.69975052983549</v>
       </c>
       <c r="E47">
-        <v>1.578500000000001</v>
+        <v>1.703800000000001</v>
       </c>
       <c r="F47">
-        <v>5.638500000000001</v>
+        <v>5.763800000000001</v>
       </c>
       <c r="G47">
         <v>0.132</v>
@@ -5129,28 +5129,28 @@
         <v>3.13</v>
       </c>
       <c r="M47">
-        <v>0.2920743</v>
+        <v>0.2985648400000001</v>
       </c>
       <c r="N47">
-        <v>2.8379257</v>
+        <v>2.83143516</v>
       </c>
       <c r="O47">
-        <v>0.822998453</v>
+        <v>0.8211161963999999</v>
       </c>
       <c r="P47">
-        <v>2.014927247</v>
+        <v>2.0103189636</v>
       </c>
       <c r="Q47">
-        <v>2.734927247</v>
+        <v>2.7303189636</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3492848288757922</v>
+        <v>0.3538739760762227</v>
       </c>
       <c r="T47">
-        <v>1.856075434179979</v>
+        <v>1.884142087179101</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.71645125914879</v>
+        <v>10.48348492742816</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2080098270811603</v>
+        <v>0.2073628982806348</v>
       </c>
       <c r="C48">
-        <v>9.067950529835485</v>
+        <v>9.001511147461768</v>
       </c>
       <c r="D48">
-        <v>14.69975052983549</v>
+        <v>14.75861114746177</v>
       </c>
       <c r="E48">
-        <v>1.703800000000001</v>
+        <v>1.829100000000001</v>
       </c>
       <c r="F48">
-        <v>5.763800000000001</v>
+        <v>5.889100000000001</v>
       </c>
       <c r="G48">
         <v>0.132</v>
@@ -5211,28 +5211,28 @@
         <v>3.13</v>
       </c>
       <c r="M48">
-        <v>0.2985648400000001</v>
+        <v>0.30505538</v>
       </c>
       <c r="N48">
-        <v>2.83143516</v>
+        <v>2.82494462</v>
       </c>
       <c r="O48">
-        <v>0.8211161963999999</v>
+        <v>0.8192339397999998</v>
       </c>
       <c r="P48">
-        <v>2.0103189636</v>
+        <v>2.0057106802</v>
       </c>
       <c r="Q48">
-        <v>2.7303189636</v>
+        <v>2.7257106802</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3538739760762227</v>
+        <v>0.3586362986427071</v>
       </c>
       <c r="T48">
-        <v>1.884142087179101</v>
+        <v>1.913267859159322</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.48348492742816</v>
+        <v>10.26043205663181</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2073628982806348</v>
+        <v>0.2067159694801093</v>
       </c>
       <c r="C49">
-        <v>9.001511147461768</v>
+        <v>8.935545038547261</v>
       </c>
       <c r="D49">
-        <v>14.75861114746177</v>
+        <v>14.81794503854726</v>
       </c>
       <c r="E49">
-        <v>1.829100000000001</v>
+        <v>1.954400000000001</v>
       </c>
       <c r="F49">
-        <v>5.889100000000001</v>
+        <v>6.014400000000001</v>
       </c>
       <c r="G49">
         <v>0.132</v>
@@ -5293,28 +5293,28 @@
         <v>3.13</v>
       </c>
       <c r="M49">
-        <v>0.30505538</v>
+        <v>0.31154592</v>
       </c>
       <c r="N49">
-        <v>2.82494462</v>
+        <v>2.81845408</v>
       </c>
       <c r="O49">
-        <v>0.8192339397999998</v>
+        <v>0.8173516832</v>
       </c>
       <c r="P49">
-        <v>2.0057106802</v>
+        <v>2.0011023968</v>
       </c>
       <c r="Q49">
-        <v>2.7257106802</v>
+        <v>2.7211023968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3586362986427071</v>
+        <v>0.3635817874617487</v>
       </c>
       <c r="T49">
-        <v>1.913267859159322</v>
+        <v>1.943513853138783</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.26043205663181</v>
+        <v>10.04667305545198</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2067159694801093</v>
+        <v>0.2060690406795839</v>
       </c>
       <c r="C50">
-        <v>8.935545038547261</v>
+        <v>8.870057934221879</v>
       </c>
       <c r="D50">
-        <v>14.81794503854726</v>
+        <v>14.87775793422188</v>
       </c>
       <c r="E50">
-        <v>1.954400000000001</v>
+        <v>2.079700000000001</v>
       </c>
       <c r="F50">
-        <v>6.0144</v>
+        <v>6.1397</v>
       </c>
       <c r="G50">
         <v>0.132</v>
@@ -5375,28 +5375,28 @@
         <v>3.13</v>
       </c>
       <c r="M50">
-        <v>0.31154592</v>
+        <v>0.31803646</v>
       </c>
       <c r="N50">
-        <v>2.81845408</v>
+        <v>2.81196354</v>
       </c>
       <c r="O50">
-        <v>0.8173516832</v>
+        <v>0.8154694265999999</v>
       </c>
       <c r="P50">
-        <v>2.0011023968</v>
+        <v>1.9964941134</v>
       </c>
       <c r="Q50">
-        <v>2.7211023968</v>
+        <v>2.7164941134</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3635817874617487</v>
+        <v>0.3687212170187919</v>
       </c>
       <c r="T50">
-        <v>1.943513853138783</v>
+        <v>1.974945964529202</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.04667305545199</v>
+        <v>9.841638911463169</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2060690406795839</v>
+        <v>0.2060256118790584</v>
       </c>
       <c r="C51">
-        <v>8.870057934221879</v>
+        <v>8.748790517864496</v>
       </c>
       <c r="D51">
-        <v>14.87775793422188</v>
+        <v>14.8817905178645</v>
       </c>
       <c r="E51">
-        <v>2.079700000000001</v>
+        <v>2.205000000000001</v>
       </c>
       <c r="F51">
-        <v>6.1397</v>
+        <v>6.265000000000001</v>
       </c>
       <c r="G51">
         <v>0.132</v>
@@ -5457,45 +5457,45 @@
         <v>3.13</v>
       </c>
       <c r="M51">
-        <v>0.31803646</v>
+        <v>0.3351775</v>
       </c>
       <c r="N51">
-        <v>2.81196354</v>
+        <v>2.7948225</v>
       </c>
       <c r="O51">
-        <v>0.8154694265999999</v>
+        <v>0.810498525</v>
       </c>
       <c r="P51">
-        <v>1.9964941134</v>
+        <v>1.984323975</v>
       </c>
       <c r="Q51">
-        <v>2.7164941134</v>
+        <v>2.704323975</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3687212170187919</v>
+        <v>0.3740662237581168</v>
       </c>
       <c r="T51">
-        <v>1.974945964529202</v>
+        <v>2.007635360375239</v>
       </c>
       <c r="U51">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V51">
         <v>0.29</v>
       </c>
       <c r="W51">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>9.841638911463169</v>
+        <v>9.338335657972268</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2060256118790584</v>
+        <v>0.2053907530785329</v>
       </c>
       <c r="C52">
-        <v>8.748790517864496</v>
+        <v>8.682690913223201</v>
       </c>
       <c r="D52">
-        <v>14.8817905178645</v>
+        <v>14.9409909132232</v>
       </c>
       <c r="E52">
-        <v>2.205000000000001</v>
+        <v>2.330300000000001</v>
       </c>
       <c r="F52">
-        <v>6.265000000000001</v>
+        <v>6.390300000000001</v>
       </c>
       <c r="G52">
         <v>0.132</v>
@@ -5539,28 +5539,28 @@
         <v>3.13</v>
       </c>
       <c r="M52">
-        <v>0.3351775</v>
+        <v>0.34188105</v>
       </c>
       <c r="N52">
-        <v>2.7948225</v>
+        <v>2.78811895</v>
       </c>
       <c r="O52">
-        <v>0.810498525</v>
+        <v>0.8085544954999999</v>
       </c>
       <c r="P52">
-        <v>1.984323975</v>
+        <v>1.9795644545</v>
       </c>
       <c r="Q52">
-        <v>2.704323975</v>
+        <v>2.6995644545</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3740662237581168</v>
+        <v>0.3796293940378223</v>
       </c>
       <c r="T52">
-        <v>2.007635360375239</v>
+        <v>2.041659017276215</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.338335657972268</v>
+        <v>9.155231037227713</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2053907530785329</v>
+        <v>0.2047558942780075</v>
       </c>
       <c r="C53">
-        <v>8.682690913223201</v>
+        <v>8.617064193115803</v>
       </c>
       <c r="D53">
-        <v>14.9409909132232</v>
+        <v>15.0006641931158</v>
       </c>
       <c r="E53">
-        <v>2.330300000000001</v>
+        <v>2.455600000000001</v>
       </c>
       <c r="F53">
-        <v>6.390300000000001</v>
+        <v>6.515600000000001</v>
       </c>
       <c r="G53">
         <v>0.132</v>
@@ -5621,28 +5621,28 @@
         <v>3.13</v>
       </c>
       <c r="M53">
-        <v>0.34188105</v>
+        <v>0.3485846</v>
       </c>
       <c r="N53">
-        <v>2.78811895</v>
+        <v>2.7814154</v>
       </c>
       <c r="O53">
-        <v>0.8085544954999999</v>
+        <v>0.8066104659999999</v>
       </c>
       <c r="P53">
-        <v>1.9795644545</v>
+        <v>1.974804934</v>
       </c>
       <c r="Q53">
-        <v>2.6995644545</v>
+        <v>2.694804934</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3796293940378223</v>
+        <v>0.3854243630791823</v>
       </c>
       <c r="T53">
-        <v>2.041659017276215</v>
+        <v>2.077100326548066</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.155231037227713</v>
+        <v>8.979168901896411</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2047558942780075</v>
+        <v>0.204121035477482</v>
       </c>
       <c r="C54">
-        <v>8.617064193115803</v>
+        <v>8.551916046266619</v>
       </c>
       <c r="D54">
-        <v>15.0006641931158</v>
+        <v>15.06081604626662</v>
       </c>
       <c r="E54">
-        <v>2.455600000000001</v>
+        <v>2.580900000000002</v>
       </c>
       <c r="F54">
-        <v>6.515600000000001</v>
+        <v>6.640900000000001</v>
       </c>
       <c r="G54">
         <v>0.132</v>
@@ -5703,28 +5703,28 @@
         <v>3.13</v>
       </c>
       <c r="M54">
-        <v>0.3485846</v>
+        <v>0.3552881500000001</v>
       </c>
       <c r="N54">
-        <v>2.7814154</v>
+        <v>2.77471185</v>
       </c>
       <c r="O54">
-        <v>0.8066104659999999</v>
+        <v>0.8046664364999998</v>
       </c>
       <c r="P54">
-        <v>1.974804934</v>
+        <v>1.9700454135</v>
       </c>
       <c r="Q54">
-        <v>2.694804934</v>
+        <v>2.6900454135</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3854243630791823</v>
+        <v>0.3914659265478341</v>
       </c>
       <c r="T54">
-        <v>2.077100326548066</v>
+        <v>2.114049776639996</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.979168901896411</v>
+        <v>8.809750620728552</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.204121035477482</v>
+        <v>0.2034861766769565</v>
       </c>
       <c r="C55">
-        <v>8.551916046266619</v>
+        <v>8.487252253013239</v>
       </c>
       <c r="D55">
-        <v>15.06081604626662</v>
+        <v>15.12145225301324</v>
       </c>
       <c r="E55">
-        <v>2.580900000000002</v>
+        <v>2.706200000000002</v>
       </c>
       <c r="F55">
-        <v>6.640900000000001</v>
+        <v>6.766200000000001</v>
       </c>
       <c r="G55">
         <v>0.132</v>
@@ -5785,28 +5785,28 @@
         <v>3.13</v>
       </c>
       <c r="M55">
-        <v>0.3552881500000001</v>
+        <v>0.3619917000000001</v>
       </c>
       <c r="N55">
-        <v>2.77471185</v>
+        <v>2.7680083</v>
       </c>
       <c r="O55">
-        <v>0.8046664364999998</v>
+        <v>0.802722407</v>
       </c>
       <c r="P55">
-        <v>1.9700454135</v>
+        <v>1.965285893</v>
       </c>
       <c r="Q55">
-        <v>2.6900454135</v>
+        <v>2.685285893</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3914659265478341</v>
+        <v>0.397770166689036</v>
       </c>
       <c r="T55">
-        <v>2.114049776639996</v>
+        <v>2.152605724562009</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.809750620728552</v>
+        <v>8.646607090715062</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2034861766769565</v>
+        <v>0.2028513178764311</v>
       </c>
       <c r="C56">
-        <v>8.487252253013239</v>
+        <v>8.423078687158185</v>
       </c>
       <c r="D56">
-        <v>15.12145225301324</v>
+        <v>15.18257868715819</v>
       </c>
       <c r="E56">
-        <v>2.706200000000002</v>
+        <v>2.831500000000002</v>
       </c>
       <c r="F56">
-        <v>6.766200000000001</v>
+        <v>6.891500000000002</v>
       </c>
       <c r="G56">
         <v>0.132</v>
@@ -5867,28 +5867,28 @@
         <v>3.13</v>
       </c>
       <c r="M56">
-        <v>0.3619917000000001</v>
+        <v>0.3686952500000001</v>
       </c>
       <c r="N56">
-        <v>2.7680083</v>
+        <v>2.76130475</v>
       </c>
       <c r="O56">
-        <v>0.802722407</v>
+        <v>0.8007783774999999</v>
       </c>
       <c r="P56">
-        <v>1.965285893</v>
+        <v>1.9605263725</v>
       </c>
       <c r="Q56">
-        <v>2.685285893</v>
+        <v>2.6805263725</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.397770166689036</v>
+        <v>0.404354595280958</v>
       </c>
       <c r="T56">
-        <v>2.152605724562009</v>
+        <v>2.192875270169445</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.646607090715062</v>
+        <v>8.489396052702059</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2028513178764311</v>
+        <v>0.2022164590759056</v>
       </c>
       <c r="C57">
-        <v>8.423078687158185</v>
+        <v>8.359401317865705</v>
       </c>
       <c r="D57">
-        <v>15.18257868715819</v>
+        <v>15.24420131786571</v>
       </c>
       <c r="E57">
-        <v>2.831500000000002</v>
+        <v>2.956800000000002</v>
       </c>
       <c r="F57">
-        <v>6.891500000000002</v>
+        <v>7.016800000000002</v>
       </c>
       <c r="G57">
         <v>0.132</v>
@@ -5949,28 +5949,28 @@
         <v>3.13</v>
       </c>
       <c r="M57">
-        <v>0.3686952500000001</v>
+        <v>0.3753988000000001</v>
       </c>
       <c r="N57">
-        <v>2.76130475</v>
+        <v>2.7546012</v>
       </c>
       <c r="O57">
-        <v>0.8007783774999999</v>
+        <v>0.7988343479999999</v>
       </c>
       <c r="P57">
-        <v>1.9605263725</v>
+        <v>1.955766852</v>
       </c>
       <c r="Q57">
-        <v>2.6805263725</v>
+        <v>2.675766852</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.404354595280958</v>
+        <v>0.4112383160816038</v>
       </c>
       <c r="T57">
-        <v>2.192875270169445</v>
+        <v>2.234975249668129</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.489396052702059</v>
+        <v>8.337799694618095</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2022164590759056</v>
+        <v>0.2015816002753802</v>
       </c>
       <c r="C58">
-        <v>8.359401317865705</v>
+        <v>8.296226211604894</v>
       </c>
       <c r="D58">
-        <v>15.24420131786571</v>
+        <v>15.3063262116049</v>
       </c>
       <c r="E58">
-        <v>2.956800000000002</v>
+        <v>3.082100000000001</v>
       </c>
       <c r="F58">
-        <v>7.016800000000002</v>
+        <v>7.142100000000001</v>
       </c>
       <c r="G58">
         <v>0.132</v>
@@ -6031,28 +6031,28 @@
         <v>3.13</v>
       </c>
       <c r="M58">
-        <v>0.3753988000000001</v>
+        <v>0.38210235</v>
       </c>
       <c r="N58">
-        <v>2.7546012</v>
+        <v>2.74789765</v>
       </c>
       <c r="O58">
-        <v>0.7988343479999999</v>
+        <v>0.7968903184999998</v>
       </c>
       <c r="P58">
-        <v>1.955766852</v>
+        <v>1.9510073315</v>
       </c>
       <c r="Q58">
-        <v>2.675766852</v>
+        <v>2.6710073315</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4112383160816038</v>
+        <v>0.4184422099427447</v>
       </c>
       <c r="T58">
-        <v>2.234975249668129</v>
+        <v>2.279033367748146</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.337799694618095</v>
+        <v>8.191522506993216</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2015816002753802</v>
+        <v>0.2009467414748547</v>
       </c>
       <c r="C59">
-        <v>8.296226211604894</v>
+        <v>8.233559534140554</v>
       </c>
       <c r="D59">
-        <v>15.3063262116049</v>
+        <v>15.36895953414056</v>
       </c>
       <c r="E59">
-        <v>3.082100000000001</v>
+        <v>3.207400000000002</v>
       </c>
       <c r="F59">
-        <v>7.142100000000001</v>
+        <v>7.267400000000001</v>
       </c>
       <c r="G59">
         <v>0.132</v>
@@ -6113,28 +6113,28 @@
         <v>3.13</v>
       </c>
       <c r="M59">
-        <v>0.38210235</v>
+        <v>0.3888059</v>
       </c>
       <c r="N59">
-        <v>2.74789765</v>
+        <v>2.7411941</v>
       </c>
       <c r="O59">
-        <v>0.7968903184999998</v>
+        <v>0.794946289</v>
       </c>
       <c r="P59">
-        <v>1.9510073315</v>
+        <v>1.946247811</v>
       </c>
       <c r="Q59">
-        <v>2.6710073315</v>
+        <v>2.666247811</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4184422099427447</v>
+        <v>0.4259891463687017</v>
       </c>
       <c r="T59">
-        <v>2.279033367748146</v>
+        <v>2.325189491451022</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.191522506993216</v>
+        <v>8.050289360320921</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2009467414748547</v>
+        <v>0.2003118826743293</v>
       </c>
       <c r="C60">
-        <v>8.233559534140554</v>
+        <v>8.171407552573118</v>
       </c>
       <c r="D60">
-        <v>15.36895953414055</v>
+        <v>15.43210755257312</v>
       </c>
       <c r="E60">
-        <v>3.207400000000001</v>
+        <v>3.332700000000001</v>
       </c>
       <c r="F60">
-        <v>7.2674</v>
+        <v>7.3927</v>
       </c>
       <c r="G60">
         <v>0.132</v>
@@ -6195,28 +6195,28 @@
         <v>3.13</v>
       </c>
       <c r="M60">
-        <v>0.3888059</v>
+        <v>0.39550945</v>
       </c>
       <c r="N60">
-        <v>2.7411941</v>
+        <v>2.73449055</v>
       </c>
       <c r="O60">
-        <v>0.794946289</v>
+        <v>0.7930022594999999</v>
       </c>
       <c r="P60">
-        <v>1.946247811</v>
+        <v>1.9414882905</v>
       </c>
       <c r="Q60">
-        <v>2.666247811</v>
+        <v>2.6614882905</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4259891463687017</v>
+        <v>0.4339042260349494</v>
       </c>
       <c r="T60">
-        <v>2.325189491451021</v>
+        <v>2.373597133383305</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.050289360320921</v>
+        <v>7.913843777942599</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2003118826743293</v>
+        <v>0.1996770238738038</v>
       </c>
       <c r="C61">
-        <v>8.171407552573118</v>
+        <v>8.1097766374291</v>
       </c>
       <c r="D61">
-        <v>15.43210755257312</v>
+        <v>15.4957766374291</v>
       </c>
       <c r="E61">
-        <v>3.332700000000001</v>
+        <v>3.458000000000001</v>
       </c>
       <c r="F61">
-        <v>7.3927</v>
+        <v>7.518000000000001</v>
       </c>
       <c r="G61">
         <v>0.132</v>
@@ -6277,28 +6277,28 @@
         <v>3.13</v>
       </c>
       <c r="M61">
-        <v>0.39550945</v>
+        <v>0.402213</v>
       </c>
       <c r="N61">
-        <v>2.73449055</v>
+        <v>2.727787</v>
       </c>
       <c r="O61">
-        <v>0.7930022594999999</v>
+        <v>0.7910582299999999</v>
       </c>
       <c r="P61">
-        <v>1.9414882905</v>
+        <v>1.93672877</v>
       </c>
       <c r="Q61">
-        <v>2.6614882905</v>
+        <v>2.65672877</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4339042260349494</v>
+        <v>0.4422150596845094</v>
       </c>
       <c r="T61">
-        <v>2.373597133383305</v>
+        <v>2.424425157412203</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.913843777942599</v>
+        <v>7.781946381643555</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1996770238738038</v>
+        <v>0.1990421650732783</v>
       </c>
       <c r="C62">
-        <v>8.1097766374291</v>
+        <v>8.048673264803455</v>
       </c>
       <c r="D62">
-        <v>15.4957766374291</v>
+        <v>15.55997326480345</v>
       </c>
       <c r="E62">
-        <v>3.458000000000001</v>
+        <v>3.583300000000001</v>
       </c>
       <c r="F62">
-        <v>7.518000000000001</v>
+        <v>7.643300000000001</v>
       </c>
       <c r="G62">
         <v>0.132</v>
@@ -6359,28 +6359,28 @@
         <v>3.13</v>
       </c>
       <c r="M62">
-        <v>0.402213</v>
+        <v>0.40891655</v>
       </c>
       <c r="N62">
-        <v>2.727787</v>
+        <v>2.72108345</v>
       </c>
       <c r="O62">
-        <v>0.7910582299999999</v>
+        <v>0.7891142004999999</v>
       </c>
       <c r="P62">
-        <v>1.93672877</v>
+        <v>1.9319692495</v>
       </c>
       <c r="Q62">
-        <v>2.65672877</v>
+        <v>2.6519692495</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4422150596845094</v>
+        <v>0.4509520899314829</v>
       </c>
       <c r="T62">
-        <v>2.424425157412203</v>
+        <v>2.477859746775917</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.781946381643555</v>
+        <v>7.654373490141203</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1990421650732783</v>
+        <v>0.1987594662727528</v>
       </c>
       <c r="C63">
-        <v>8.048673264803455</v>
+        <v>7.952131117359794</v>
       </c>
       <c r="D63">
-        <v>15.55997326480345</v>
+        <v>15.5887311173598</v>
       </c>
       <c r="E63">
-        <v>3.583300000000001</v>
+        <v>3.708600000000001</v>
       </c>
       <c r="F63">
-        <v>7.643300000000001</v>
+        <v>7.768600000000001</v>
       </c>
       <c r="G63">
         <v>0.132</v>
@@ -6441,45 +6441,45 @@
         <v>3.13</v>
       </c>
       <c r="M63">
-        <v>0.40891655</v>
+        <v>0.4218349800000001</v>
       </c>
       <c r="N63">
-        <v>2.72108345</v>
+        <v>2.70816502</v>
       </c>
       <c r="O63">
-        <v>0.7891142004999999</v>
+        <v>0.7853678557999999</v>
       </c>
       <c r="P63">
-        <v>1.9319692495</v>
+        <v>1.9227971642</v>
       </c>
       <c r="Q63">
-        <v>2.6519692495</v>
+        <v>2.6427971642</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4509520899314829</v>
+        <v>0.4601489638756654</v>
       </c>
       <c r="T63">
-        <v>2.477859746775917</v>
+        <v>2.534106682948246</v>
       </c>
       <c r="U63">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V63">
         <v>0.29</v>
       </c>
       <c r="W63">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y63">
-        <v>7.654373490141203</v>
+        <v>7.419963133450905</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1987594662727528</v>
+        <v>0.1981302874722274</v>
       </c>
       <c r="C64">
-        <v>7.952131117359794</v>
+        <v>7.891218175960482</v>
       </c>
       <c r="D64">
-        <v>15.5887311173598</v>
+        <v>15.65311817596048</v>
       </c>
       <c r="E64">
-        <v>3.708600000000001</v>
+        <v>3.833900000000001</v>
       </c>
       <c r="F64">
-        <v>7.768600000000001</v>
+        <v>7.8939</v>
       </c>
       <c r="G64">
         <v>0.132</v>
@@ -6523,28 +6523,28 @@
         <v>3.13</v>
       </c>
       <c r="M64">
-        <v>0.4218349800000001</v>
+        <v>0.42863877</v>
       </c>
       <c r="N64">
-        <v>2.70816502</v>
+        <v>2.70136123</v>
       </c>
       <c r="O64">
-        <v>0.7853678557999999</v>
+        <v>0.7833947566999999</v>
       </c>
       <c r="P64">
-        <v>1.9227971642</v>
+        <v>1.9179664733</v>
       </c>
       <c r="Q64">
-        <v>2.6427971642</v>
+        <v>2.6379664733</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4601489638756654</v>
+        <v>0.4698429661411552</v>
       </c>
       <c r="T64">
-        <v>2.534106682948246</v>
+        <v>2.593393994048811</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.419963133450905</v>
+        <v>7.302185940856446</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1981302874722274</v>
+        <v>0.1975011086717019</v>
       </c>
       <c r="C65">
-        <v>7.891218175960482</v>
+        <v>7.830839323898482</v>
       </c>
       <c r="D65">
-        <v>15.65311817596048</v>
+        <v>15.71803932389848</v>
       </c>
       <c r="E65">
-        <v>3.833900000000001</v>
+        <v>3.959200000000002</v>
       </c>
       <c r="F65">
-        <v>7.8939</v>
+        <v>8.019200000000001</v>
       </c>
       <c r="G65">
         <v>0.132</v>
@@ -6605,28 +6605,28 @@
         <v>3.13</v>
       </c>
       <c r="M65">
-        <v>0.42863877</v>
+        <v>0.4354425600000001</v>
       </c>
       <c r="N65">
-        <v>2.70136123</v>
+        <v>2.69455744</v>
       </c>
       <c r="O65">
-        <v>0.7833947566999999</v>
+        <v>0.7814216575999998</v>
       </c>
       <c r="P65">
-        <v>1.9179664733</v>
+        <v>1.9131357824</v>
       </c>
       <c r="Q65">
-        <v>2.6379664733</v>
+        <v>2.6331357824</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4698429661411552</v>
+        <v>0.480075524088061</v>
       </c>
       <c r="T65">
-        <v>2.593393994048811</v>
+        <v>2.655975044654962</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.302185940856446</v>
+        <v>7.188089285530562</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1975011086717019</v>
+        <v>0.1968719298711765</v>
       </c>
       <c r="C66">
-        <v>7.830839323898482</v>
+        <v>7.771001234240499</v>
       </c>
       <c r="D66">
-        <v>15.71803932389848</v>
+        <v>15.7835012342405</v>
       </c>
       <c r="E66">
-        <v>3.959200000000002</v>
+        <v>4.084500000000001</v>
       </c>
       <c r="F66">
-        <v>8.019200000000001</v>
+        <v>8.144500000000001</v>
       </c>
       <c r="G66">
         <v>0.132</v>
@@ -6687,28 +6687,28 @@
         <v>3.13</v>
       </c>
       <c r="M66">
-        <v>0.4354425600000001</v>
+        <v>0.4422463500000001</v>
       </c>
       <c r="N66">
-        <v>2.69455744</v>
+        <v>2.68775365</v>
       </c>
       <c r="O66">
-        <v>0.7814216575999998</v>
+        <v>0.7794485584999999</v>
       </c>
       <c r="P66">
-        <v>1.9131357824</v>
+        <v>1.9083050915</v>
       </c>
       <c r="Q66">
-        <v>2.6331357824</v>
+        <v>2.6283050915</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.480075524088061</v>
+        <v>0.4908927996319328</v>
       </c>
       <c r="T66">
-        <v>2.655975044654962</v>
+        <v>2.722132155295749</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.188089285530562</v>
+        <v>7.077503296522401</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1968719298711765</v>
+        <v>0.196242751070651</v>
       </c>
       <c r="C67">
-        <v>7.771001234240499</v>
+        <v>7.711710691685127</v>
       </c>
       <c r="D67">
-        <v>15.7835012342405</v>
+        <v>15.84951069168513</v>
       </c>
       <c r="E67">
-        <v>4.084500000000001</v>
+        <v>4.209800000000002</v>
       </c>
       <c r="F67">
-        <v>8.144500000000001</v>
+        <v>8.269800000000002</v>
       </c>
       <c r="G67">
         <v>0.132</v>
@@ -6769,28 +6769,28 @@
         <v>3.13</v>
       </c>
       <c r="M67">
-        <v>0.4422463500000001</v>
+        <v>0.4490501400000001</v>
       </c>
       <c r="N67">
-        <v>2.68775365</v>
+        <v>2.68094986</v>
       </c>
       <c r="O67">
-        <v>0.7794485584999999</v>
+        <v>0.7774754593999998</v>
       </c>
       <c r="P67">
-        <v>1.9083050915</v>
+        <v>1.9034744006</v>
       </c>
       <c r="Q67">
-        <v>2.6283050915</v>
+        <v>2.6234744006</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4908927996319328</v>
+        <v>0.5023463855019148</v>
       </c>
       <c r="T67">
-        <v>2.722132155295749</v>
+        <v>2.792180860680114</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.077503296522401</v>
+        <v>6.970268398090242</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.196242751070651</v>
+        <v>0.1956135722701255</v>
       </c>
       <c r="C68">
-        <v>7.711710691685127</v>
+        <v>7.652974594906995</v>
       </c>
       <c r="D68">
-        <v>15.84951069168513</v>
+        <v>15.91607459490699</v>
       </c>
       <c r="E68">
-        <v>4.209800000000002</v>
+        <v>4.335100000000002</v>
       </c>
       <c r="F68">
-        <v>8.269800000000002</v>
+        <v>8.395100000000001</v>
       </c>
       <c r="G68">
         <v>0.132</v>
@@ -6851,28 +6851,28 @@
         <v>3.13</v>
       </c>
       <c r="M68">
-        <v>0.4490501400000001</v>
+        <v>0.4558539300000001</v>
       </c>
       <c r="N68">
-        <v>2.68094986</v>
+        <v>2.67414607</v>
       </c>
       <c r="O68">
-        <v>0.7774754593999998</v>
+        <v>0.7755023603</v>
       </c>
       <c r="P68">
-        <v>1.9034744006</v>
+        <v>1.8986437097</v>
       </c>
       <c r="Q68">
-        <v>2.6234744006</v>
+        <v>2.6186437097</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5023463855019148</v>
+        <v>0.5144941280912896</v>
       </c>
       <c r="T68">
-        <v>2.792180860680114</v>
+        <v>2.866474942148378</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.970268398090242</v>
+        <v>6.86623454140233</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1956135722701255</v>
+        <v>0.1949843934696001</v>
       </c>
       <c r="C69">
-        <v>7.652974594906995</v>
+        <v>7.594799958960156</v>
       </c>
       <c r="D69">
-        <v>15.91607459490699</v>
+        <v>15.98319995896016</v>
       </c>
       <c r="E69">
-        <v>4.335100000000002</v>
+        <v>4.460400000000003</v>
       </c>
       <c r="F69">
-        <v>8.395100000000001</v>
+        <v>8.520400000000002</v>
       </c>
       <c r="G69">
         <v>0.132</v>
@@ -6933,28 +6933,28 @@
         <v>3.13</v>
       </c>
       <c r="M69">
-        <v>0.4558539300000001</v>
+        <v>0.4626577200000001</v>
       </c>
       <c r="N69">
-        <v>2.67414607</v>
+        <v>2.66734228</v>
       </c>
       <c r="O69">
-        <v>0.7755023603</v>
+        <v>0.7735292611999999</v>
       </c>
       <c r="P69">
-        <v>1.8986437097</v>
+        <v>1.8938130188</v>
       </c>
       <c r="Q69">
-        <v>2.6186437097</v>
+        <v>2.6138130188</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5144941280912896</v>
+        <v>0.5274011045925003</v>
       </c>
       <c r="T69">
-        <v>2.866474942148378</v>
+        <v>2.94541240370841</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.86623454140233</v>
+        <v>6.765260504028765</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1949843934696001</v>
+        <v>0.1943552146690746</v>
       </c>
       <c r="C70">
-        <v>7.594799958960156</v>
+        <v>7.53719391774268</v>
       </c>
       <c r="D70">
-        <v>15.98319995896016</v>
+        <v>16.05089391774268</v>
       </c>
       <c r="E70">
-        <v>4.460400000000003</v>
+        <v>4.585700000000002</v>
       </c>
       <c r="F70">
-        <v>8.520400000000002</v>
+        <v>8.645700000000001</v>
       </c>
       <c r="G70">
         <v>0.132</v>
@@ -7015,28 +7015,28 @@
         <v>3.13</v>
       </c>
       <c r="M70">
-        <v>0.4626577200000001</v>
+        <v>0.4694615100000001</v>
       </c>
       <c r="N70">
-        <v>2.66734228</v>
+        <v>2.66053849</v>
       </c>
       <c r="O70">
-        <v>0.7735292611999999</v>
+        <v>0.7715561620999999</v>
       </c>
       <c r="P70">
-        <v>1.8938130188</v>
+        <v>1.8889823279</v>
       </c>
       <c r="Q70">
-        <v>2.6138130188</v>
+        <v>2.6089823279</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5274011045925003</v>
+        <v>0.5411407892550796</v>
       </c>
       <c r="T70">
-        <v>2.94541240370841</v>
+        <v>3.029442604723927</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.765260504028765</v>
+        <v>6.667213250347189</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1943552146690746</v>
+        <v>0.1937260358685491</v>
       </c>
       <c r="C71">
-        <v>7.53719391774268</v>
+        <v>7.480163726524019</v>
       </c>
       <c r="D71">
-        <v>16.05089391774268</v>
+        <v>16.11916372652402</v>
       </c>
       <c r="E71">
-        <v>4.585700000000002</v>
+        <v>4.711000000000001</v>
       </c>
       <c r="F71">
-        <v>8.645700000000001</v>
+        <v>8.771000000000001</v>
       </c>
       <c r="G71">
         <v>0.132</v>
@@ -7097,28 +7097,28 @@
         <v>3.13</v>
       </c>
       <c r="M71">
-        <v>0.4694615100000001</v>
+        <v>0.4762653000000001</v>
       </c>
       <c r="N71">
-        <v>2.66053849</v>
+        <v>2.6537347</v>
       </c>
       <c r="O71">
-        <v>0.7715561620999999</v>
+        <v>0.7695830629999999</v>
       </c>
       <c r="P71">
-        <v>1.8889823279</v>
+        <v>1.884151637</v>
       </c>
       <c r="Q71">
-        <v>2.6089823279</v>
+        <v>2.604151637</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5411407892550796</v>
+        <v>0.555796452895164</v>
       </c>
       <c r="T71">
-        <v>3.029442604723927</v>
+        <v>3.119074819140478</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.667213250347189</v>
+        <v>6.5719673467708</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1937260358685491</v>
+        <v>0.1930968570680237</v>
       </c>
       <c r="C72">
-        <v>7.480163726524019</v>
+        <v>7.423716764537206</v>
       </c>
       <c r="D72">
-        <v>16.11916372652402</v>
+        <v>16.18801676453721</v>
       </c>
       <c r="E72">
-        <v>4.711000000000001</v>
+        <v>4.836300000000002</v>
       </c>
       <c r="F72">
-        <v>8.771000000000001</v>
+        <v>8.896300000000002</v>
       </c>
       <c r="G72">
         <v>0.132</v>
@@ -7179,28 +7179,28 @@
         <v>3.13</v>
       </c>
       <c r="M72">
-        <v>0.4762653000000001</v>
+        <v>0.4830690900000001</v>
       </c>
       <c r="N72">
-        <v>2.6537347</v>
+        <v>2.64693091</v>
       </c>
       <c r="O72">
-        <v>0.7695830629999999</v>
+        <v>0.7676099638999999</v>
       </c>
       <c r="P72">
-        <v>1.884151637</v>
+        <v>1.8793209461</v>
       </c>
       <c r="Q72">
-        <v>2.604151637</v>
+        <v>2.5993209461</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.555796452895164</v>
+        <v>0.5714628519587025</v>
       </c>
       <c r="T72">
-        <v>3.119074819140478</v>
+        <v>3.214888565585758</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.5719673467708</v>
+        <v>6.479404426393748</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1930968570680237</v>
+        <v>0.1924676782674982</v>
       </c>
       <c r="C73">
-        <v>7.423716764537204</v>
+        <v>7.367860537637787</v>
       </c>
       <c r="D73">
-        <v>16.1880167645372</v>
+        <v>16.25746053763779</v>
       </c>
       <c r="E73">
-        <v>4.8363</v>
+        <v>4.961600000000002</v>
       </c>
       <c r="F73">
-        <v>8.8963</v>
+        <v>9.021600000000001</v>
       </c>
       <c r="G73">
         <v>0.132</v>
@@ -7261,28 +7261,28 @@
         <v>3.13</v>
       </c>
       <c r="M73">
-        <v>0.48306909</v>
+        <v>0.4898728800000001</v>
       </c>
       <c r="N73">
-        <v>2.64693091</v>
+        <v>2.64012712</v>
       </c>
       <c r="O73">
-        <v>0.7676099638999999</v>
+        <v>0.7656368647999999</v>
       </c>
       <c r="P73">
-        <v>1.8793209461</v>
+        <v>1.8744902552</v>
       </c>
       <c r="Q73">
-        <v>2.5993209461</v>
+        <v>2.5944902552</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5714628519587024</v>
+        <v>0.5882482795267794</v>
       </c>
       <c r="T73">
-        <v>3.214888565585757</v>
+        <v>3.317546151062842</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.479404426393748</v>
+        <v>6.38941269824939</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1924676782674982</v>
+        <v>0.1918384994669727</v>
       </c>
       <c r="C74">
-        <v>7.367860537637787</v>
+        <v>7.312602681031459</v>
       </c>
       <c r="D74">
-        <v>16.25746053763779</v>
+        <v>16.32750268103146</v>
       </c>
       <c r="E74">
-        <v>4.961600000000002</v>
+        <v>5.086900000000001</v>
       </c>
       <c r="F74">
-        <v>9.021600000000001</v>
+        <v>9.1469</v>
       </c>
       <c r="G74">
         <v>0.132</v>
@@ -7343,28 +7343,28 @@
         <v>3.13</v>
       </c>
       <c r="M74">
-        <v>0.4898728800000001</v>
+        <v>0.49667667</v>
       </c>
       <c r="N74">
-        <v>2.64012712</v>
+        <v>2.63332333</v>
       </c>
       <c r="O74">
-        <v>0.7656368647999999</v>
+        <v>0.7636637656999998</v>
       </c>
       <c r="P74">
-        <v>1.8744902552</v>
+        <v>1.8696595643</v>
       </c>
       <c r="Q74">
-        <v>2.5944902552</v>
+        <v>2.5896595643</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5882482795267794</v>
+        <v>0.606277072099899</v>
       </c>
       <c r="T74">
-        <v>3.317546151062842</v>
+        <v>3.427808002130821</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.38941269824939</v>
+        <v>6.301886496903507</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1918384994669727</v>
+        <v>0.1912093206664473</v>
       </c>
       <c r="C75">
-        <v>7.312602681031459</v>
+        <v>7.257950962072478</v>
       </c>
       <c r="D75">
-        <v>16.32750268103146</v>
+        <v>16.39815096207248</v>
       </c>
       <c r="E75">
-        <v>5.086900000000001</v>
+        <v>5.212200000000002</v>
       </c>
       <c r="F75">
-        <v>9.1469</v>
+        <v>9.272200000000002</v>
       </c>
       <c r="G75">
         <v>0.132</v>
@@ -7425,28 +7425,28 @@
         <v>3.13</v>
       </c>
       <c r="M75">
-        <v>0.49667667</v>
+        <v>0.5034804600000001</v>
       </c>
       <c r="N75">
-        <v>2.63332333</v>
+        <v>2.62651954</v>
       </c>
       <c r="O75">
-        <v>0.7636637656999998</v>
+        <v>0.7616906666</v>
       </c>
       <c r="P75">
-        <v>1.8696595643</v>
+        <v>1.8648288734</v>
       </c>
       <c r="Q75">
-        <v>2.5896595643</v>
+        <v>2.5848288734</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.606277072099899</v>
+        <v>0.6256926948709511</v>
       </c>
       <c r="T75">
-        <v>3.427808002130821</v>
+        <v>3.546551534050185</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.301886496903507</v>
+        <v>6.216725868566973</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1912093206664473</v>
+        <v>0.1905801418659218</v>
       </c>
       <c r="C76">
-        <v>7.257950962072478</v>
+        <v>7.203913283135176</v>
       </c>
       <c r="D76">
-        <v>16.39815096207248</v>
+        <v>16.46941328313518</v>
       </c>
       <c r="E76">
-        <v>5.212200000000002</v>
+        <v>5.337500000000001</v>
       </c>
       <c r="F76">
-        <v>9.272200000000002</v>
+        <v>9.397500000000001</v>
       </c>
       <c r="G76">
         <v>0.132</v>
@@ -7507,28 +7507,28 @@
         <v>3.13</v>
       </c>
       <c r="M76">
-        <v>0.5034804600000001</v>
+        <v>0.5102842500000001</v>
       </c>
       <c r="N76">
-        <v>2.62651954</v>
+        <v>2.61971575</v>
       </c>
       <c r="O76">
-        <v>0.7616906666</v>
+        <v>0.7597175674999999</v>
       </c>
       <c r="P76">
-        <v>1.8648288734</v>
+        <v>1.8599981825</v>
       </c>
       <c r="Q76">
-        <v>2.5848288734</v>
+        <v>2.5799981825</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6256926948709511</v>
+        <v>0.6466615674636874</v>
       </c>
       <c r="T76">
-        <v>3.546551534050185</v>
+        <v>3.674794548523098</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.216725868566973</v>
+        <v>6.133836190319413</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1905801418659218</v>
+        <v>0.1904905630653964</v>
       </c>
       <c r="C77">
-        <v>7.203913283135176</v>
+        <v>7.088809596260269</v>
       </c>
       <c r="D77">
-        <v>16.46941328313518</v>
+        <v>16.47960959626027</v>
       </c>
       <c r="E77">
-        <v>5.337500000000001</v>
+        <v>5.462800000000001</v>
       </c>
       <c r="F77">
-        <v>9.397500000000001</v>
+        <v>9.5228</v>
       </c>
       <c r="G77">
         <v>0.132</v>
@@ -7589,45 +7589,45 @@
         <v>3.13</v>
       </c>
       <c r="M77">
-        <v>0.5102842500000001</v>
+        <v>0.52661084</v>
       </c>
       <c r="N77">
-        <v>2.61971575</v>
+        <v>2.60338916</v>
       </c>
       <c r="O77">
-        <v>0.7597175674999999</v>
+        <v>0.7549828564</v>
       </c>
       <c r="P77">
-        <v>1.8599981825</v>
+        <v>1.8484063036</v>
       </c>
       <c r="Q77">
-        <v>2.5799981825</v>
+        <v>2.5684063036</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6466615674636874</v>
+        <v>0.6693778461058184</v>
       </c>
       <c r="T77">
-        <v>3.674794548523098</v>
+        <v>3.813724480868753</v>
       </c>
       <c r="U77">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V77">
         <v>0.29</v>
       </c>
       <c r="W77">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>6.133836190319413</v>
+        <v>5.943668003491914</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1904905630653964</v>
+        <v>0.1898684842648709</v>
       </c>
       <c r="C78">
-        <v>7.088809596260269</v>
+        <v>7.034667530787592</v>
       </c>
       <c r="D78">
-        <v>16.47960959626027</v>
+        <v>16.55076753078759</v>
       </c>
       <c r="E78">
-        <v>5.462800000000001</v>
+        <v>5.588100000000002</v>
       </c>
       <c r="F78">
-        <v>9.5228</v>
+        <v>9.648100000000001</v>
       </c>
       <c r="G78">
         <v>0.132</v>
@@ -7671,28 +7671,28 @@
         <v>3.13</v>
       </c>
       <c r="M78">
-        <v>0.52661084</v>
+        <v>0.5335399300000001</v>
       </c>
       <c r="N78">
-        <v>2.60338916</v>
+        <v>2.59646007</v>
       </c>
       <c r="O78">
-        <v>0.7549828564</v>
+        <v>0.7529734202999999</v>
       </c>
       <c r="P78">
-        <v>1.8484063036</v>
+        <v>1.8434866497</v>
       </c>
       <c r="Q78">
-        <v>2.5684063036</v>
+        <v>2.5634866497</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6693778461058184</v>
+        <v>0.6940694533255258</v>
       </c>
       <c r="T78">
-        <v>3.813724480868753</v>
+        <v>3.964735276896638</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.943668003491914</v>
+        <v>5.86647750994007</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1898684842648709</v>
+        <v>0.1892464054643455</v>
       </c>
       <c r="C79">
-        <v>7.034667530787592</v>
+        <v>6.981142641359371</v>
       </c>
       <c r="D79">
-        <v>16.55076753078759</v>
+        <v>16.62254264135937</v>
       </c>
       <c r="E79">
-        <v>5.588100000000002</v>
+        <v>5.713400000000001</v>
       </c>
       <c r="F79">
-        <v>9.648100000000001</v>
+        <v>9.773400000000001</v>
       </c>
       <c r="G79">
         <v>0.132</v>
@@ -7753,28 +7753,28 @@
         <v>3.13</v>
       </c>
       <c r="M79">
-        <v>0.5335399300000001</v>
+        <v>0.5404690200000001</v>
       </c>
       <c r="N79">
-        <v>2.59646007</v>
+        <v>2.58953098</v>
       </c>
       <c r="O79">
-        <v>0.7529734202999999</v>
+        <v>0.7509639841999999</v>
       </c>
       <c r="P79">
-        <v>1.8434866497</v>
+        <v>1.8385669958</v>
       </c>
       <c r="Q79">
-        <v>2.5634866497</v>
+        <v>2.5585669958</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6940694533255258</v>
+        <v>0.7210057521106613</v>
       </c>
       <c r="T79">
-        <v>3.964735276896638</v>
+        <v>4.129474327108878</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.86647750994007</v>
+        <v>5.791266259812633</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1892464054643455</v>
+        <v>0.18862432666382</v>
       </c>
       <c r="C80">
-        <v>6.981142641359371</v>
+        <v>6.928242992402925</v>
       </c>
       <c r="D80">
-        <v>16.62254264135937</v>
+        <v>16.69494299240293</v>
       </c>
       <c r="E80">
-        <v>5.713400000000001</v>
+        <v>5.838700000000002</v>
       </c>
       <c r="F80">
-        <v>9.773400000000001</v>
+        <v>9.898700000000002</v>
       </c>
       <c r="G80">
         <v>0.132</v>
@@ -7835,28 +7835,28 @@
         <v>3.13</v>
       </c>
       <c r="M80">
-        <v>0.5404690200000001</v>
+        <v>0.5473981100000002</v>
       </c>
       <c r="N80">
-        <v>2.58953098</v>
+        <v>2.58260189</v>
       </c>
       <c r="O80">
-        <v>0.7509639841999999</v>
+        <v>0.7489545481</v>
       </c>
       <c r="P80">
-        <v>1.8385669958</v>
+        <v>1.8336473419</v>
       </c>
       <c r="Q80">
-        <v>2.5585669958</v>
+        <v>2.5536473419</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7210057521106613</v>
+        <v>0.7505074126848573</v>
       </c>
       <c r="T80">
-        <v>4.129474327108878</v>
+        <v>4.309902810674664</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.791266259812633</v>
+        <v>5.717959091966903</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.18862432666382</v>
+        <v>0.1880022478632945</v>
       </c>
       <c r="C81">
-        <v>6.928242992402925</v>
+        <v>6.875976789460339</v>
       </c>
       <c r="D81">
-        <v>16.69494299240293</v>
+        <v>16.76797678946034</v>
       </c>
       <c r="E81">
-        <v>5.838700000000002</v>
+        <v>5.964000000000001</v>
       </c>
       <c r="F81">
-        <v>9.898700000000002</v>
+        <v>10.024</v>
       </c>
       <c r="G81">
         <v>0.132</v>
@@ -7917,28 +7917,28 @@
         <v>3.13</v>
       </c>
       <c r="M81">
-        <v>0.5473981100000002</v>
+        <v>0.5543272</v>
       </c>
       <c r="N81">
-        <v>2.58260189</v>
+        <v>2.5756728</v>
       </c>
       <c r="O81">
-        <v>0.7489545481</v>
+        <v>0.7469451119999999</v>
       </c>
       <c r="P81">
-        <v>1.8336473419</v>
+        <v>1.828727688</v>
       </c>
       <c r="Q81">
-        <v>2.5536473419</v>
+        <v>2.548727688</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7505074126848573</v>
+        <v>0.7829592393164728</v>
       </c>
       <c r="T81">
-        <v>4.309902810674664</v>
+        <v>4.508374142597027</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.717959091966903</v>
+        <v>5.646484603317319</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1880022478632945</v>
+        <v>0.1873801690627691</v>
       </c>
       <c r="C82">
-        <v>6.875976789460339</v>
+        <v>6.8243523822886</v>
       </c>
       <c r="D82">
-        <v>16.76797678946034</v>
+        <v>16.8416523822886</v>
       </c>
       <c r="E82">
-        <v>5.964000000000001</v>
+        <v>6.089300000000002</v>
       </c>
       <c r="F82">
-        <v>10.024</v>
+        <v>10.1493</v>
       </c>
       <c r="G82">
         <v>0.132</v>
@@ -7999,28 +7999,28 @@
         <v>3.13</v>
       </c>
       <c r="M82">
-        <v>0.5543272</v>
+        <v>0.5612562900000001</v>
       </c>
       <c r="N82">
-        <v>2.5756728</v>
+        <v>2.56874371</v>
       </c>
       <c r="O82">
-        <v>0.7469451119999999</v>
+        <v>0.7449356758999999</v>
       </c>
       <c r="P82">
-        <v>1.828727688</v>
+        <v>1.8238080341</v>
       </c>
       <c r="Q82">
-        <v>2.548727688</v>
+        <v>2.5438080341</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.7829592393164728</v>
+        <v>0.8188270476987849</v>
       </c>
       <c r="T82">
-        <v>4.508374142597027</v>
+        <v>4.727737193669115</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.646484603317319</v>
+        <v>5.57677491685661</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1873801690627691</v>
+        <v>0.1867580902622436</v>
       </c>
       <c r="C83">
-        <v>6.8243523822886</v>
+        <v>6.773378268041951</v>
       </c>
       <c r="D83">
-        <v>16.8416523822886</v>
+        <v>16.91597826804195</v>
       </c>
       <c r="E83">
-        <v>6.089300000000002</v>
+        <v>6.214600000000002</v>
       </c>
       <c r="F83">
-        <v>10.1493</v>
+        <v>10.2746</v>
       </c>
       <c r="G83">
         <v>0.132</v>
@@ -8081,28 +8081,28 @@
         <v>3.13</v>
       </c>
       <c r="M83">
-        <v>0.5612562900000001</v>
+        <v>0.5681853800000001</v>
       </c>
       <c r="N83">
-        <v>2.56874371</v>
+        <v>2.56181462</v>
       </c>
       <c r="O83">
-        <v>0.7449356758999999</v>
+        <v>0.7429262397999999</v>
       </c>
       <c r="P83">
-        <v>1.8238080341</v>
+        <v>1.8188883802</v>
       </c>
       <c r="Q83">
-        <v>2.5438080341</v>
+        <v>2.5388883802</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8188270476987849</v>
+        <v>0.8586801681235759</v>
       </c>
       <c r="T83">
-        <v>4.727737193669115</v>
+        <v>4.971473917082545</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.57677491685661</v>
+        <v>5.508765466651042</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1867580902622436</v>
+        <v>0.1861360114617181</v>
       </c>
       <c r="C84">
-        <v>6.773378268041951</v>
+        <v>6.723063094538666</v>
       </c>
       <c r="D84">
-        <v>16.91597826804195</v>
+        <v>16.99096309453867</v>
       </c>
       <c r="E84">
-        <v>6.214600000000002</v>
+        <v>6.339900000000003</v>
       </c>
       <c r="F84">
-        <v>10.2746</v>
+        <v>10.3999</v>
       </c>
       <c r="G84">
         <v>0.132</v>
@@ -8163,28 +8163,28 @@
         <v>3.13</v>
       </c>
       <c r="M84">
-        <v>0.5681853800000001</v>
+        <v>0.5751144700000002</v>
       </c>
       <c r="N84">
-        <v>2.56181462</v>
+        <v>2.55488553</v>
       </c>
       <c r="O84">
-        <v>0.7429262397999999</v>
+        <v>0.7409168036999999</v>
       </c>
       <c r="P84">
-        <v>1.8188883802</v>
+        <v>1.8139687263</v>
       </c>
       <c r="Q84">
-        <v>2.5388883802</v>
+        <v>2.5339687263</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.8586801681235759</v>
+        <v>0.9032218909512835</v>
       </c>
       <c r="T84">
-        <v>4.971473917082545</v>
+        <v>5.243885549132848</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.508765466651042</v>
+        <v>5.442394798378137</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1861360114617181</v>
+        <v>0.1855139326611927</v>
       </c>
       <c r="C85">
-        <v>6.723063094538666</v>
+        <v>6.673415663615327</v>
       </c>
       <c r="D85">
-        <v>16.99096309453867</v>
+        <v>17.06661566361533</v>
       </c>
       <c r="E85">
-        <v>6.339900000000003</v>
+        <v>6.465200000000002</v>
       </c>
       <c r="F85">
-        <v>10.3999</v>
+        <v>10.5252</v>
       </c>
       <c r="G85">
         <v>0.132</v>
@@ -8245,28 +8245,28 @@
         <v>3.13</v>
       </c>
       <c r="M85">
-        <v>0.5751144700000002</v>
+        <v>0.5820435600000001</v>
       </c>
       <c r="N85">
-        <v>2.55488553</v>
+        <v>2.54795644</v>
       </c>
       <c r="O85">
-        <v>0.7409168036999999</v>
+        <v>0.7389073675999999</v>
       </c>
       <c r="P85">
-        <v>1.8139687263</v>
+        <v>1.8090490724</v>
       </c>
       <c r="Q85">
-        <v>2.5339687263</v>
+        <v>2.529049072399999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9032218909512835</v>
+        <v>0.9533313291324549</v>
       </c>
       <c r="T85">
-        <v>5.243885549132848</v>
+        <v>5.550348635189442</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.442394798378137</v>
+        <v>5.377604384111731</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1855139326611927</v>
+        <v>0.1848918538606673</v>
       </c>
       <c r="C86">
-        <v>6.673415663615328</v>
+        <v>6.624444934570946</v>
       </c>
       <c r="D86">
-        <v>17.06661566361533</v>
+        <v>17.14294493457095</v>
       </c>
       <c r="E86">
-        <v>6.4652</v>
+        <v>6.590500000000001</v>
       </c>
       <c r="F86">
-        <v>10.5252</v>
+        <v>10.6505</v>
       </c>
       <c r="G86">
         <v>0.132</v>
@@ -8327,28 +8327,28 @@
         <v>3.13</v>
       </c>
       <c r="M86">
-        <v>0.58204356</v>
+        <v>0.5889726500000001</v>
       </c>
       <c r="N86">
-        <v>2.54795644</v>
+        <v>2.54102735</v>
       </c>
       <c r="O86">
-        <v>0.7389073676</v>
+        <v>0.7368979314999999</v>
       </c>
       <c r="P86">
-        <v>1.8090490724</v>
+        <v>1.8041294185</v>
       </c>
       <c r="Q86">
-        <v>2.5290490724</v>
+        <v>2.5241294185</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.9533313291324542</v>
+        <v>1.010122025737782</v>
       </c>
       <c r="T86">
-        <v>5.550348635189438</v>
+        <v>5.897673466053575</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.377604384111732</v>
+        <v>5.314338450181005</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1848918538606673</v>
+        <v>0.1842697750601418</v>
       </c>
       <c r="C87">
-        <v>6.624444934570946</v>
+        <v>6.576160027704013</v>
       </c>
       <c r="D87">
-        <v>17.14294493457095</v>
+        <v>17.21996002770401</v>
       </c>
       <c r="E87">
-        <v>6.590500000000001</v>
+        <v>6.715800000000001</v>
       </c>
       <c r="F87">
-        <v>10.6505</v>
+        <v>10.7758</v>
       </c>
       <c r="G87">
         <v>0.132</v>
@@ -8409,28 +8409,28 @@
         <v>3.13</v>
       </c>
       <c r="M87">
-        <v>0.5889726500000001</v>
+        <v>0.5959017400000001</v>
       </c>
       <c r="N87">
-        <v>2.54102735</v>
+        <v>2.53409826</v>
       </c>
       <c r="O87">
-        <v>0.7368979314999999</v>
+        <v>0.7348884953999999</v>
       </c>
       <c r="P87">
-        <v>1.8041294185</v>
+        <v>1.7992097646</v>
       </c>
       <c r="Q87">
-        <v>2.5241294185</v>
+        <v>2.5192097646</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.010122025737782</v>
+        <v>1.075025679001013</v>
       </c>
       <c r="T87">
-        <v>5.897673466053575</v>
+        <v>6.294616129898304</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.314338450181005</v>
+        <v>5.252543817039365</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1842697750601418</v>
+        <v>0.1836476962596164</v>
       </c>
       <c r="C88">
-        <v>6.576160027704013</v>
+        <v>6.528570227945268</v>
       </c>
       <c r="D88">
-        <v>17.21996002770401</v>
+        <v>17.29767022794527</v>
       </c>
       <c r="E88">
-        <v>6.715800000000001</v>
+        <v>6.841100000000002</v>
       </c>
       <c r="F88">
-        <v>10.7758</v>
+        <v>10.9011</v>
       </c>
       <c r="G88">
         <v>0.132</v>
@@ -8491,28 +8491,28 @@
         <v>3.13</v>
       </c>
       <c r="M88">
-        <v>0.5959017400000001</v>
+        <v>0.6028308300000002</v>
       </c>
       <c r="N88">
-        <v>2.53409826</v>
+        <v>2.52716917</v>
       </c>
       <c r="O88">
-        <v>0.7348884953999999</v>
+        <v>0.7328790592999999</v>
       </c>
       <c r="P88">
-        <v>1.7992097646</v>
+        <v>1.7942901107</v>
       </c>
       <c r="Q88">
-        <v>2.5192097646</v>
+        <v>2.5142901107</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.075025679001013</v>
+        <v>1.149914509689356</v>
       </c>
       <c r="T88">
-        <v>6.294616129898304</v>
+        <v>6.75262689587299</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.252543817039365</v>
+        <v>5.192169750176843</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1836476962596164</v>
+        <v>0.1830256174590909</v>
       </c>
       <c r="C89">
-        <v>6.528570227945268</v>
+        <v>6.481684988589306</v>
       </c>
       <c r="D89">
-        <v>17.29767022794527</v>
+        <v>17.37608498858931</v>
       </c>
       <c r="E89">
-        <v>6.841100000000002</v>
+        <v>6.966400000000001</v>
       </c>
       <c r="F89">
-        <v>10.9011</v>
+        <v>11.0264</v>
       </c>
       <c r="G89">
         <v>0.132</v>
@@ -8573,28 +8573,28 @@
         <v>3.13</v>
       </c>
       <c r="M89">
-        <v>0.6028308300000002</v>
+        <v>0.60975992</v>
       </c>
       <c r="N89">
-        <v>2.52716917</v>
+        <v>2.52024008</v>
       </c>
       <c r="O89">
-        <v>0.7328790592999999</v>
+        <v>0.7308696231999999</v>
       </c>
       <c r="P89">
-        <v>1.7942901107</v>
+        <v>1.7893704568</v>
       </c>
       <c r="Q89">
-        <v>2.5142901107</v>
+        <v>2.5093704568</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.149914509689356</v>
+        <v>1.237284812159091</v>
       </c>
       <c r="T89">
-        <v>6.75262689587299</v>
+        <v>7.286972789510126</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.192169750176843</v>
+        <v>5.133167821197562</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1830256174590909</v>
+        <v>0.1824035386585654</v>
       </c>
       <c r="C90">
-        <v>6.481684988589306</v>
+        <v>6.435513935128149</v>
       </c>
       <c r="D90">
-        <v>17.37608498858931</v>
+        <v>17.45521393512815</v>
       </c>
       <c r="E90">
-        <v>6.966400000000001</v>
+        <v>7.091700000000002</v>
       </c>
       <c r="F90">
-        <v>11.0264</v>
+        <v>11.1517</v>
       </c>
       <c r="G90">
         <v>0.132</v>
@@ -8655,28 +8655,28 @@
         <v>3.13</v>
       </c>
       <c r="M90">
-        <v>0.60975992</v>
+        <v>0.6166890100000001</v>
       </c>
       <c r="N90">
-        <v>2.52024008</v>
+        <v>2.51331099</v>
       </c>
       <c r="O90">
-        <v>0.7308696231999999</v>
+        <v>0.7288601870999999</v>
       </c>
       <c r="P90">
-        <v>1.7893704568</v>
+        <v>1.7844508029</v>
       </c>
       <c r="Q90">
-        <v>2.5093704568</v>
+        <v>2.5044508029</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.237284812159091</v>
+        <v>1.340540624168777</v>
       </c>
       <c r="T90">
-        <v>7.286972789510126</v>
+        <v>7.918472481990376</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.133167821197562</v>
+        <v>5.075491778262758</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1824035386585654</v>
+        <v>0.18178145985804</v>
       </c>
       <c r="C91">
-        <v>6.435513935128149</v>
+        <v>6.390066869190015</v>
       </c>
       <c r="D91">
-        <v>17.45521393512815</v>
+        <v>17.53506686919001</v>
       </c>
       <c r="E91">
-        <v>7.091700000000002</v>
+        <v>7.217000000000001</v>
       </c>
       <c r="F91">
-        <v>11.1517</v>
+        <v>11.277</v>
       </c>
       <c r="G91">
         <v>0.132</v>
@@ -8737,28 +8737,28 @@
         <v>3.13</v>
       </c>
       <c r="M91">
-        <v>0.6166890100000001</v>
+        <v>0.6236181000000001</v>
       </c>
       <c r="N91">
-        <v>2.51331099</v>
+        <v>2.5063819</v>
       </c>
       <c r="O91">
-        <v>0.7288601870999999</v>
+        <v>0.726850751</v>
       </c>
       <c r="P91">
-        <v>1.7844508029</v>
+        <v>1.779531149</v>
       </c>
       <c r="Q91">
-        <v>2.5044508029</v>
+        <v>2.499531149</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.340540624168777</v>
+        <v>1.4644475985804</v>
       </c>
       <c r="T91">
-        <v>7.918472481990376</v>
+        <v>8.676272112966675</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.075491778262758</v>
+        <v>5.019097425170949</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.18178145985804</v>
+        <v>0.1811593810575145</v>
       </c>
       <c r="C92">
-        <v>6.390066869190015</v>
+        <v>6.345353772586718</v>
       </c>
       <c r="D92">
-        <v>17.53506686919001</v>
+        <v>17.61565377258672</v>
       </c>
       <c r="E92">
-        <v>7.217000000000001</v>
+        <v>7.342300000000002</v>
       </c>
       <c r="F92">
-        <v>11.277</v>
+        <v>11.4023</v>
       </c>
       <c r="G92">
         <v>0.132</v>
@@ -8819,28 +8819,28 @@
         <v>3.13</v>
       </c>
       <c r="M92">
-        <v>0.6236181000000001</v>
+        <v>0.6305471900000001</v>
       </c>
       <c r="N92">
-        <v>2.5063819</v>
+        <v>2.49945281</v>
       </c>
       <c r="O92">
-        <v>0.726850751</v>
+        <v>0.7248413148999999</v>
       </c>
       <c r="P92">
-        <v>1.779531149</v>
+        <v>1.7746114951</v>
       </c>
       <c r="Q92">
-        <v>2.499531149</v>
+        <v>2.4946114951</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.4644475985804</v>
+        <v>1.615889456194606</v>
       </c>
       <c r="T92">
-        <v>8.676272112966675</v>
+        <v>9.602471661937711</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.019097425170949</v>
+        <v>4.963942508410828</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1811593810575145</v>
+        <v>0.1805373022569891</v>
       </c>
       <c r="C93">
-        <v>6.345353772586718</v>
+        <v>6.301384811473193</v>
       </c>
       <c r="D93">
-        <v>17.61565377258672</v>
+        <v>17.69698481147319</v>
       </c>
       <c r="E93">
-        <v>7.342300000000002</v>
+        <v>7.467600000000002</v>
       </c>
       <c r="F93">
-        <v>11.4023</v>
+        <v>11.5276</v>
       </c>
       <c r="G93">
         <v>0.132</v>
@@ -8901,28 +8901,28 @@
         <v>3.13</v>
       </c>
       <c r="M93">
-        <v>0.6305471900000001</v>
+        <v>0.6374762800000001</v>
       </c>
       <c r="N93">
-        <v>2.49945281</v>
+        <v>2.49252372</v>
       </c>
       <c r="O93">
-        <v>0.7248413148999999</v>
+        <v>0.7228318787999999</v>
       </c>
       <c r="P93">
-        <v>1.7746114951</v>
+        <v>1.7696918412</v>
       </c>
       <c r="Q93">
-        <v>2.4946114951</v>
+        <v>2.4896918412</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.615889456194606</v>
+        <v>1.805191778212364</v>
       </c>
       <c r="T93">
-        <v>9.602471661937711</v>
+        <v>10.7602210981515</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.963942508410828</v>
+        <v>4.909986611580276</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1805373022569891</v>
+        <v>0.1799152234564635</v>
       </c>
       <c r="C94">
-        <v>6.301384811473193</v>
+        <v>6.258170340622783</v>
       </c>
       <c r="D94">
-        <v>17.69698481147319</v>
+        <v>17.77907034062278</v>
       </c>
       <c r="E94">
-        <v>7.467600000000002</v>
+        <v>7.592900000000003</v>
       </c>
       <c r="F94">
-        <v>11.5276</v>
+        <v>11.6529</v>
       </c>
       <c r="G94">
         <v>0.132</v>
@@ -8983,28 +8983,28 @@
         <v>3.13</v>
       </c>
       <c r="M94">
-        <v>0.6374762800000001</v>
+        <v>0.6444053700000002</v>
       </c>
       <c r="N94">
-        <v>2.49252372</v>
+        <v>2.48559463</v>
       </c>
       <c r="O94">
-        <v>0.7228318787999999</v>
+        <v>0.7208224426999998</v>
       </c>
       <c r="P94">
-        <v>1.7696918412</v>
+        <v>1.7647721873</v>
       </c>
       <c r="Q94">
-        <v>2.4896918412</v>
+        <v>2.4847721873</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.805191778212364</v>
+        <v>2.04858047794948</v>
       </c>
       <c r="T94">
-        <v>10.7602210981515</v>
+        <v>12.24875608756924</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.909986611580276</v>
+        <v>4.857191056617046</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1799152234564635</v>
+        <v>0.1792931446559381</v>
       </c>
       <c r="C95">
-        <v>6.258170340622783</v>
+        <v>6.215720907822003</v>
       </c>
       <c r="D95">
-        <v>17.77907034062278</v>
+        <v>17.861920907822</v>
       </c>
       <c r="E95">
-        <v>7.592900000000003</v>
+        <v>7.718200000000002</v>
       </c>
       <c r="F95">
-        <v>11.6529</v>
+        <v>11.7782</v>
       </c>
       <c r="G95">
         <v>0.132</v>
@@ -9065,28 +9065,28 @@
         <v>3.13</v>
       </c>
       <c r="M95">
-        <v>0.6444053700000002</v>
+        <v>0.6513344600000002</v>
       </c>
       <c r="N95">
-        <v>2.48559463</v>
+        <v>2.47866554</v>
       </c>
       <c r="O95">
-        <v>0.7208224426999998</v>
+        <v>0.7188130065999999</v>
       </c>
       <c r="P95">
-        <v>1.7647721873</v>
+        <v>1.7598525334</v>
       </c>
       <c r="Q95">
-        <v>2.4847721873</v>
+        <v>2.4798525334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.04858047794948</v>
+        <v>2.373098744265637</v>
       </c>
       <c r="T95">
-        <v>12.24875608756924</v>
+        <v>14.23346940679288</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.857191056617046</v>
+        <v>4.805518811333886</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1792931446559381</v>
+        <v>0.1786710658554126</v>
       </c>
       <c r="C96">
-        <v>6.215720907822003</v>
+        <v>6.174047258388882</v>
       </c>
       <c r="D96">
-        <v>17.861920907822</v>
+        <v>17.94554725838888</v>
       </c>
       <c r="E96">
-        <v>7.718200000000002</v>
+        <v>7.843500000000001</v>
       </c>
       <c r="F96">
-        <v>11.7782</v>
+        <v>11.9035</v>
       </c>
       <c r="G96">
         <v>0.132</v>
@@ -9147,28 +9147,28 @@
         <v>3.13</v>
       </c>
       <c r="M96">
-        <v>0.6513344600000002</v>
+        <v>0.65826355</v>
       </c>
       <c r="N96">
-        <v>2.47866554</v>
+        <v>2.47173645</v>
       </c>
       <c r="O96">
-        <v>0.7188130065999999</v>
+        <v>0.7168035704999999</v>
       </c>
       <c r="P96">
-        <v>1.7598525334</v>
+        <v>1.7549328795</v>
       </c>
       <c r="Q96">
-        <v>2.4798525334</v>
+        <v>2.4749328795</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.373098744265637</v>
+        <v>2.827424317108256</v>
       </c>
       <c r="T96">
-        <v>14.23346940679288</v>
+        <v>17.01206805370599</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.805518811333886</v>
+        <v>4.754934402793531</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1786710658554126</v>
+        <v>0.1780489870548871</v>
       </c>
       <c r="C97">
-        <v>6.174047258388882</v>
+        <v>6.133160339818671</v>
       </c>
       <c r="D97">
-        <v>17.94554725838888</v>
+        <v>18.02996033981867</v>
       </c>
       <c r="E97">
-        <v>7.843500000000001</v>
+        <v>7.968800000000003</v>
       </c>
       <c r="F97">
-        <v>11.9035</v>
+        <v>12.0288</v>
       </c>
       <c r="G97">
         <v>0.132</v>
@@ -9229,28 +9229,28 @@
         <v>3.13</v>
       </c>
       <c r="M97">
-        <v>0.65826355</v>
+        <v>0.6651926400000001</v>
       </c>
       <c r="N97">
-        <v>2.47173645</v>
+        <v>2.46480736</v>
       </c>
       <c r="O97">
-        <v>0.7168035704999999</v>
+        <v>0.7147941343999999</v>
       </c>
       <c r="P97">
-        <v>1.7549328795</v>
+        <v>1.7500132256</v>
       </c>
       <c r="Q97">
-        <v>2.4749328795</v>
+        <v>2.4700132256</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.827424317108256</v>
+        <v>3.508912676372185</v>
       </c>
       <c r="T97">
-        <v>17.01206805370599</v>
+        <v>21.17996602407565</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.754934402793531</v>
+        <v>4.705403836097765</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1780489870548872</v>
+        <v>0.1774269082543617</v>
       </c>
       <c r="C98">
-        <v>6.133160339818666</v>
+        <v>6.093071306561436</v>
       </c>
       <c r="D98">
-        <v>18.02996033981866</v>
+        <v>18.11517130656144</v>
       </c>
       <c r="E98">
-        <v>7.968800000000001</v>
+        <v>8.094100000000001</v>
       </c>
       <c r="F98">
-        <v>12.0288</v>
+        <v>12.1541</v>
       </c>
       <c r="G98">
         <v>0.132</v>
@@ -9311,28 +9311,28 @@
         <v>3.13</v>
       </c>
       <c r="M98">
-        <v>0.66519264</v>
+        <v>0.6721217300000001</v>
       </c>
       <c r="N98">
-        <v>2.46480736</v>
+        <v>2.45787827</v>
       </c>
       <c r="O98">
-        <v>0.7147941343999999</v>
+        <v>0.7127846982999999</v>
       </c>
       <c r="P98">
-        <v>1.7500132256</v>
+        <v>1.7450935717</v>
       </c>
       <c r="Q98">
-        <v>2.4700132256</v>
+        <v>2.4650935717</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.508912676372177</v>
+        <v>4.644726608478719</v>
       </c>
       <c r="T98">
-        <v>21.1799660240756</v>
+        <v>28.12646264135834</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.705403836097766</v>
+        <v>4.65689451819985</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1774269082543617</v>
+        <v>0.1768048294538362</v>
       </c>
       <c r="C99">
-        <v>6.093071306561436</v>
+        <v>6.053791524935681</v>
       </c>
       <c r="D99">
-        <v>18.11517130656144</v>
+        <v>18.20119152493568</v>
       </c>
       <c r="E99">
-        <v>8.094100000000001</v>
+        <v>8.2194</v>
       </c>
       <c r="F99">
-        <v>12.1541</v>
+        <v>12.2794</v>
       </c>
       <c r="G99">
         <v>0.132</v>
@@ -9393,28 +9393,28 @@
         <v>3.13</v>
       </c>
       <c r="M99">
-        <v>0.6721217300000001</v>
+        <v>0.6790508200000001</v>
       </c>
       <c r="N99">
-        <v>2.45787827</v>
+        <v>2.45094918</v>
       </c>
       <c r="O99">
-        <v>0.7127846982999999</v>
+        <v>0.7107752621999999</v>
       </c>
       <c r="P99">
-        <v>1.7450935717</v>
+        <v>1.7401739178</v>
       </c>
       <c r="Q99">
-        <v>2.4650935717</v>
+        <v>2.4601739178</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.644726608478719</v>
+        <v>6.916354472691807</v>
       </c>
       <c r="T99">
-        <v>28.12646264135834</v>
+        <v>42.01945587592382</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.65689451819985</v>
+        <v>4.609375186381484</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1768048294538362</v>
+        <v>0.1761827506533108</v>
       </c>
       <c r="C100">
-        <v>6.053791524935681</v>
+        <v>6.015332578182615</v>
       </c>
       <c r="D100">
-        <v>18.20119152493568</v>
+        <v>18.28803257818262</v>
       </c>
       <c r="E100">
-        <v>8.2194</v>
+        <v>8.344700000000003</v>
       </c>
       <c r="F100">
-        <v>12.2794</v>
+        <v>12.4047</v>
       </c>
       <c r="G100">
         <v>0.132</v>
@@ -9475,28 +9475,28 @@
         <v>3.13</v>
       </c>
       <c r="M100">
-        <v>0.6790508200000001</v>
+        <v>0.6859799100000001</v>
       </c>
       <c r="N100">
-        <v>2.45094918</v>
+        <v>2.44402009</v>
       </c>
       <c r="O100">
-        <v>0.7107752621999999</v>
+        <v>0.7087658260999998</v>
       </c>
       <c r="P100">
-        <v>1.7401739178</v>
+        <v>1.7352542639</v>
       </c>
       <c r="Q100">
-        <v>2.4601739178</v>
+        <v>2.4552542639</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.916354472691807</v>
+        <v>13.73123806533107</v>
       </c>
       <c r="T100">
-        <v>42.01945587592382</v>
+        <v>83.69843557962025</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.609375186381484</v>
+        <v>4.562815841064499</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1761827506533108</v>
-      </c>
-      <c r="C101">
-        <v>6.015332578182615</v>
-      </c>
-      <c r="D101">
-        <v>18.28803257818262</v>
-      </c>
-      <c r="E101">
-        <v>8.344700000000003</v>
-      </c>
-      <c r="F101">
-        <v>12.4047</v>
-      </c>
-      <c r="G101">
-        <v>0.132</v>
-      </c>
-      <c r="H101">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.85</v>
-      </c>
-      <c r="K101">
-        <v>0.72</v>
-      </c>
-      <c r="L101">
-        <v>3.13</v>
-      </c>
-      <c r="M101">
-        <v>0.6859799100000001</v>
-      </c>
-      <c r="N101">
-        <v>2.44402009</v>
-      </c>
-      <c r="O101">
-        <v>0.7087658260999998</v>
-      </c>
-      <c r="P101">
-        <v>1.7352542639</v>
-      </c>
-      <c r="Q101">
-        <v>2.4552542639</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>13.73123806533107</v>
-      </c>
-      <c r="T101">
-        <v>83.69843557962025</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.29</v>
-      </c>
-      <c r="W101">
-        <v>0.039263</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.562815841064499</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
